--- a/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
+++ b/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projet Kicad\Barre_de_Son_Dolby_DIY\Amplificateur_Audio\Amplificateur_Audio_Custom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\le-ma\Documents\Projet electronique\Projet_Sound_Bar_DIY\Amplificateur_Audio\Amplificateur_Audio_Custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{572BC3F3-E029-4B5F-B20B-6C5FCC8CC941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F4D474-D9D3-41AF-B895-2873E91B5675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
+    <workbookView xWindow="3810" yWindow="1170" windowWidth="9620" windowHeight="12200" activeTab="1" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Condensateur" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="172">
   <si>
     <t>Ref Ti</t>
   </si>
@@ -205,6 +205,354 @@
   </si>
   <si>
     <t>GRM155R71A104KA01D</t>
+  </si>
+  <si>
+    <t>33.2k</t>
+  </si>
+  <si>
+    <t>R38</t>
+  </si>
+  <si>
+    <t>R39</t>
+  </si>
+  <si>
+    <t>R40</t>
+  </si>
+  <si>
+    <t>R42</t>
+  </si>
+  <si>
+    <t>R44</t>
+  </si>
+  <si>
+    <t>R60</t>
+  </si>
+  <si>
+    <t>R61</t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>R201</t>
+  </si>
+  <si>
+    <t>R202</t>
+  </si>
+  <si>
+    <t>R203</t>
+  </si>
+  <si>
+    <t>R204</t>
+  </si>
+  <si>
+    <t>R205</t>
+  </si>
+  <si>
+    <t>R206</t>
+  </si>
+  <si>
+    <t>R207</t>
+  </si>
+  <si>
+    <t>R208</t>
+  </si>
+  <si>
+    <t>CRCW040233K2FKED</t>
+  </si>
+  <si>
+    <t>0402</t>
+  </si>
+  <si>
+    <t>2k</t>
+  </si>
+  <si>
+    <t>R235</t>
+  </si>
+  <si>
+    <t>R234</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>ERJ-2RKF2001X</t>
+  </si>
+  <si>
+    <t>R93</t>
+  </si>
+  <si>
+    <t>R94</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>R64</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>CRCW06030000Z0EA</t>
+  </si>
+  <si>
+    <t>R232</t>
+  </si>
+  <si>
+    <t>R231</t>
+  </si>
+  <si>
+    <t>R230</t>
+  </si>
+  <si>
+    <t>R233</t>
+  </si>
+  <si>
+    <t>CRCW0402100KFKED</t>
+  </si>
+  <si>
+    <t>47.5K</t>
+  </si>
+  <si>
+    <t>R41</t>
+  </si>
+  <si>
+    <t>R74</t>
+  </si>
+  <si>
+    <t>R229</t>
+  </si>
+  <si>
+    <t>R227</t>
+  </si>
+  <si>
+    <t>CRCW040247K5FKED</t>
+  </si>
+  <si>
+    <t>R228</t>
+  </si>
+  <si>
+    <t>R43</t>
+  </si>
+  <si>
+    <t>CRCW0402332RFKED</t>
+  </si>
+  <si>
+    <t>2.15K</t>
+  </si>
+  <si>
+    <t>R50</t>
+  </si>
+  <si>
+    <t>R63</t>
+  </si>
+  <si>
+    <t>R67</t>
+  </si>
+  <si>
+    <t>R69</t>
+  </si>
+  <si>
+    <t>R71</t>
+  </si>
+  <si>
+    <t>R73</t>
+  </si>
+  <si>
+    <t>R225</t>
+  </si>
+  <si>
+    <t>R224</t>
+  </si>
+  <si>
+    <t>R226</t>
+  </si>
+  <si>
+    <t>R223</t>
+  </si>
+  <si>
+    <t>R222</t>
+  </si>
+  <si>
+    <t>R221</t>
+  </si>
+  <si>
+    <t>CRCW04022K15FKED</t>
+  </si>
+  <si>
+    <t>R220</t>
+  </si>
+  <si>
+    <t>R216</t>
+  </si>
+  <si>
+    <t>R219</t>
+  </si>
+  <si>
+    <t>R218</t>
+  </si>
+  <si>
+    <t>R217</t>
+  </si>
+  <si>
+    <t>R215</t>
+  </si>
+  <si>
+    <t>R46</t>
+  </si>
+  <si>
+    <t>R62</t>
+  </si>
+  <si>
+    <t>R65</t>
+  </si>
+  <si>
+    <t>R68</t>
+  </si>
+  <si>
+    <t>R70</t>
+  </si>
+  <si>
+    <t>R72</t>
+  </si>
+  <si>
+    <t>ERJ-2RKF1000X</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>R59</t>
+  </si>
+  <si>
+    <t>R54</t>
+  </si>
+  <si>
+    <t>R55</t>
+  </si>
+  <si>
+    <t>R56</t>
+  </si>
+  <si>
+    <t>R57</t>
+  </si>
+  <si>
+    <t>R58</t>
+  </si>
+  <si>
+    <t>R66</t>
+  </si>
+  <si>
+    <t>R209</t>
+  </si>
+  <si>
+    <t>R210</t>
+  </si>
+  <si>
+    <t>R211</t>
+  </si>
+  <si>
+    <t>R212</t>
+  </si>
+  <si>
+    <t>R213</t>
+  </si>
+  <si>
+    <t>R214</t>
+  </si>
+  <si>
+    <t>R236</t>
+  </si>
+  <si>
+    <t>CRCW040210K0FKED</t>
+  </si>
+  <si>
+    <t>CRCW060310K0FKEA</t>
+  </si>
+  <si>
+    <t>0602</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>R237</t>
+  </si>
+  <si>
+    <t>R238</t>
+  </si>
+  <si>
+    <t>R239</t>
+  </si>
+  <si>
+    <t>R240</t>
+  </si>
+  <si>
+    <t>R241</t>
+  </si>
+  <si>
+    <t>R242</t>
+  </si>
+  <si>
+    <t>R243</t>
+  </si>
+  <si>
+    <t>R244</t>
+  </si>
+  <si>
+    <t>R245</t>
+  </si>
+  <si>
+    <t>R246</t>
+  </si>
+  <si>
+    <t>R247</t>
+  </si>
+  <si>
+    <t>R248</t>
   </si>
 </sst>
 </file>
@@ -264,10 +612,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,14 +932,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A7B1A76-5DD3-4569-B12C-ED9F49EA38A1}">
   <dimension ref="A1:T34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="6" max="6" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -621,7 +965,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -659,7 +1003,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -681,7 +1025,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -694,7 +1038,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -707,7 +1051,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -720,7 +1064,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -733,7 +1077,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -746,7 +1090,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -759,7 +1103,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -788,7 +1132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -844,7 +1188,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -882,7 +1226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -917,7 +1261,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="D29" s="3"/>
       <c r="I29" s="3"/>
@@ -934,7 +1278,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="D30" s="3"/>
       <c r="I30" s="3"/>
@@ -951,7 +1295,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="D31" s="3"/>
       <c r="I31" s="3"/>
@@ -968,7 +1312,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
       <c r="D32" s="3"/>
       <c r="I32" s="3"/>
@@ -985,7 +1329,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" s="3"/>
       <c r="D33" s="3"/>
       <c r="I33" s="3"/>
@@ -1002,7 +1346,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="O34" t="s">
         <v>48</v>
       </c>
@@ -1025,9 +1369,1085 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D596A7B6-3493-4889-918C-0138A853E649}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:F111"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.6640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="3"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="3"/>
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="3"/>
+      <c r="D38" s="3"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="3"/>
+      <c r="D40" s="3"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="3"/>
+      <c r="D41" s="3"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="3"/>
+      <c r="D42" s="3"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B48" s="3"/>
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="3"/>
+      <c r="D49" s="3"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="3"/>
+      <c r="D50" s="3"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="3"/>
+      <c r="D51" s="3"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="3"/>
+      <c r="D52" s="3"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>332</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" t="s">
+        <v>99</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="3"/>
+      <c r="D58" s="3"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="3"/>
+      <c r="D59" s="3"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="3"/>
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B61" s="3"/>
+      <c r="D61" s="3"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B62" s="3"/>
+      <c r="D62" s="3"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B63" s="3"/>
+      <c r="D63" s="3"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3">
+        <v>2</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" t="s">
+        <v>109</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>104</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>105</v>
+      </c>
+      <c r="B69" s="3"/>
+      <c r="C69" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>106</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>108</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B73" s="3"/>
+      <c r="D73" s="3"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>100</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3">
+        <v>2</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F78" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" t="s">
+        <v>116</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>123</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" t="s">
+        <v>117</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>124</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" t="s">
+        <v>118</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>125</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" t="s">
+        <v>119</v>
+      </c>
+      <c r="D82" s="3"/>
+      <c r="E82" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>126</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="E83" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>127</v>
+      </c>
+      <c r="B84" s="3"/>
+      <c r="C84" t="s">
+        <v>121</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B85" s="3"/>
+      <c r="D85" s="3"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>4</v>
+      </c>
+      <c r="F88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="3">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="3">
+        <v>2</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>130</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F90" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>131</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" t="s">
+        <v>138</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F91" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>132</v>
+      </c>
+      <c r="B92" s="3"/>
+      <c r="C92" t="s">
+        <v>139</v>
+      </c>
+      <c r="D92" s="3"/>
+      <c r="E92" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F92" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>133</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" s="3"/>
+      <c r="E93" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F93" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>134</v>
+      </c>
+      <c r="B94" s="3"/>
+      <c r="C94" t="s">
+        <v>141</v>
+      </c>
+      <c r="D94" s="3"/>
+      <c r="E94" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F94" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95" s="3"/>
+      <c r="C95" t="s">
+        <v>142</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F95" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>136</v>
+      </c>
+      <c r="B96" s="3"/>
+      <c r="C96" t="s">
+        <v>143</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F96" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>147</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" s="3">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="3">
+        <v>2</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>148</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" t="s">
+        <v>160</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>149</v>
+      </c>
+      <c r="B101" s="3"/>
+      <c r="C101" t="s">
+        <v>161</v>
+      </c>
+      <c r="D101" s="3"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>150</v>
+      </c>
+      <c r="B102" s="3"/>
+      <c r="C102" t="s">
+        <v>162</v>
+      </c>
+      <c r="D102" s="3"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>151</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103" s="3"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>152</v>
+      </c>
+      <c r="B104" s="3"/>
+      <c r="C104" t="s">
+        <v>164</v>
+      </c>
+      <c r="D104" s="3"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>153</v>
+      </c>
+      <c r="B105" s="3"/>
+      <c r="C105" t="s">
+        <v>165</v>
+      </c>
+      <c r="D105" s="3"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>154</v>
+      </c>
+      <c r="B106" s="3"/>
+      <c r="C106" t="s">
+        <v>166</v>
+      </c>
+      <c r="D106" s="3"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>155</v>
+      </c>
+      <c r="C107" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>156</v>
+      </c>
+      <c r="C108" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>157</v>
+      </c>
+      <c r="C109" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>158</v>
+      </c>
+      <c r="C110" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>159</v>
+      </c>
+      <c r="C111" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B99:B106"/>
+    <mergeCell ref="D99:D106"/>
+    <mergeCell ref="B66:B73"/>
+    <mergeCell ref="D66:D73"/>
+    <mergeCell ref="B78:B85"/>
+    <mergeCell ref="D78:D85"/>
+    <mergeCell ref="B89:B96"/>
+    <mergeCell ref="D89:D96"/>
+    <mergeCell ref="B35:B42"/>
+    <mergeCell ref="D35:D42"/>
+    <mergeCell ref="B45:B52"/>
+    <mergeCell ref="D45:D52"/>
+    <mergeCell ref="B56:B63"/>
+    <mergeCell ref="D56:D63"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="D2:D9"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="D24:D31"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
+++ b/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\le-ma\Documents\Projet electronique\Projet_Sound_Bar_DIY\Amplificateur_Audio\Amplificateur_Audio_Custom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projet Kicad\Barre_de_Son_Dolby_DIY\Amplificateur_Audio\Amplificateur_Audio_Custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F4D474-D9D3-41AF-B895-2873E91B5675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE8C37D-8059-418F-AA6A-B9F8E85B6AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="1170" windowWidth="9620" windowHeight="12200" activeTab="1" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19455" windowHeight="20985" activeTab="2" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Condensateur" sheetId="1" r:id="rId1"/>
     <sheet name="Résistance" sheetId="2" r:id="rId2"/>
+    <sheet name="Autres composants" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="745">
   <si>
     <t>Ref Ti</t>
   </si>
@@ -477,9 +478,6 @@
     <t>CRCW060310K0FKEA</t>
   </si>
   <si>
-    <t>0602</t>
-  </si>
-  <si>
     <t>2K</t>
   </si>
   <si>
@@ -553,19 +551,1778 @@
   </si>
   <si>
     <t>R248</t>
+  </si>
+  <si>
+    <t>24LC512-I/ST</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>Ref carte</t>
+  </si>
+  <si>
+    <t>U203</t>
+  </si>
+  <si>
+    <t>Boitier</t>
+  </si>
+  <si>
+    <t>TSSOP-8</t>
+  </si>
+  <si>
+    <t>Verification ?</t>
+  </si>
+  <si>
+    <t>TCA9548ARGER</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>U204</t>
+  </si>
+  <si>
+    <t>RGE0024C</t>
+  </si>
+  <si>
+    <t>TCA6 4 0 8ARSVR</t>
+  </si>
+  <si>
+    <t>U202</t>
+  </si>
+  <si>
+    <t>RSV0016A</t>
+  </si>
+  <si>
+    <t>Boitier TI</t>
+  </si>
+  <si>
+    <t>Boitier Carte</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>TCA6408ARSVR:QFN40P180X260X55-16N</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>MSP430F5234IRGZT</t>
+  </si>
+  <si>
+    <t>U201</t>
+  </si>
+  <si>
+    <t>RGZ0048B</t>
+  </si>
+  <si>
+    <t>Package_DFN_QFN:Texas_RGZ0048A_VQFN-48-1EP_7x7mm_P0.5mm_EP5.15x5.15mm</t>
+  </si>
+  <si>
+    <t>(VQFN-48)</t>
+  </si>
+  <si>
+    <t>16-pin UQFN (RSV)</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>NX3215SA-32.768K-STD-MUA8</t>
+  </si>
+  <si>
+    <t>Y201</t>
+  </si>
+  <si>
+    <t>2-SMD</t>
+  </si>
+  <si>
+    <t>SMD3215-2p</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>Q7</t>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>Q206</t>
+  </si>
+  <si>
+    <t>Q202</t>
+  </si>
+  <si>
+    <t>Q204</t>
+  </si>
+  <si>
+    <t>Q205</t>
+  </si>
+  <si>
+    <t>Q203</t>
+  </si>
+  <si>
+    <t>Q201</t>
+  </si>
+  <si>
+    <t>MMBT2222A</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D206</t>
+  </si>
+  <si>
+    <t>D202</t>
+  </si>
+  <si>
+    <t>D205</t>
+  </si>
+  <si>
+    <t>D204</t>
+  </si>
+  <si>
+    <t>D203</t>
+  </si>
+  <si>
+    <t>D201</t>
+  </si>
+  <si>
+    <t>LTST-C190CKT</t>
+  </si>
+  <si>
+    <t>SMLP12BC7TT86</t>
+  </si>
+  <si>
+    <t>Blue LED</t>
+  </si>
+  <si>
+    <t>SMLD12BN1WT86C</t>
+  </si>
+  <si>
+    <t>Si ref obsolete nouvelle ref</t>
+  </si>
+  <si>
+    <t>0603 - 1608 metric</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_0603_1608Metric_Pad1.05x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>SML-P11UTT86R</t>
+  </si>
+  <si>
+    <t>0402 (1005 metric)</t>
+  </si>
+  <si>
+    <t>D,1.6x0.8x0.8mm</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_0402_1005Metric_Pad0.77x0.64mm_HandSolder</t>
+  </si>
+  <si>
+    <t>MUTE</t>
+  </si>
+  <si>
+    <t>VOL-UP</t>
+  </si>
+  <si>
+    <t>VOL-DN</t>
+  </si>
+  <si>
+    <t>MODE1</t>
+  </si>
+  <si>
+    <t>MODE2</t>
+  </si>
+  <si>
+    <t>MODE3</t>
+  </si>
+  <si>
+    <t>MODE4</t>
+  </si>
+  <si>
+    <t>LOAD</t>
+  </si>
+  <si>
+    <t>SW201</t>
+  </si>
+  <si>
+    <t>SW202</t>
+  </si>
+  <si>
+    <t>SW203</t>
+  </si>
+  <si>
+    <t>SW204</t>
+  </si>
+  <si>
+    <t>SW205</t>
+  </si>
+  <si>
+    <t>SW206</t>
+  </si>
+  <si>
+    <t>SW207</t>
+  </si>
+  <si>
+    <t>SW208</t>
+  </si>
+  <si>
+    <t>SW209</t>
+  </si>
+  <si>
+    <t>RESET</t>
+  </si>
+  <si>
+    <t>TL1015AF160QG</t>
+  </si>
+  <si>
+    <t>Switch, 4.4x2x2.9 mm</t>
+  </si>
+  <si>
+    <t>Button_Switch_SMD:SW_SPST_TL3342</t>
+  </si>
+  <si>
+    <t>USB-I2X</t>
+  </si>
+  <si>
+    <t>J203</t>
+  </si>
+  <si>
+    <t>J11</t>
+  </si>
+  <si>
+    <t>JTAG</t>
+  </si>
+  <si>
+    <t>J201</t>
+  </si>
+  <si>
+    <t>J202</t>
+  </si>
+  <si>
+    <t>PPPC082LFBN-RC</t>
+  </si>
+  <si>
+    <t>Receptacle, 2.54mm, 8x2, TH</t>
+  </si>
+  <si>
+    <t>PBC02SAAN</t>
+  </si>
+  <si>
+    <t>Sullins 100mil, 1x2, 230 mil above insulator</t>
+  </si>
+  <si>
+    <t>851-43-006-10-001000</t>
+  </si>
+  <si>
+    <t>Receptacle, 6x1, 50mil, TH</t>
+  </si>
+  <si>
+    <t>Faire le jtag sur le pcb</t>
+  </si>
+  <si>
+    <t>PinHeader_2x08_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>PinHeader_1x02_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>PinSocket_1x06_P1.27mm_Vertical</t>
+  </si>
+  <si>
+    <t>C301</t>
+  </si>
+  <si>
+    <t>C302</t>
+  </si>
+  <si>
+    <t>C303</t>
+  </si>
+  <si>
+    <t>C304</t>
+  </si>
+  <si>
+    <t>C305</t>
+  </si>
+  <si>
+    <t>C306</t>
+  </si>
+  <si>
+    <t>C307</t>
+  </si>
+  <si>
+    <t>C308</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>R25</t>
+  </si>
+  <si>
+    <t>R29</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>R31</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>R33</t>
+  </si>
+  <si>
+    <t>R322</t>
+  </si>
+  <si>
+    <t>R323</t>
+  </si>
+  <si>
+    <t>R324</t>
+  </si>
+  <si>
+    <t>R325</t>
+  </si>
+  <si>
+    <t>R326</t>
+  </si>
+  <si>
+    <t>R327</t>
+  </si>
+  <si>
+    <t>R328</t>
+  </si>
+  <si>
+    <t>R329</t>
+  </si>
+  <si>
+    <t>R330</t>
+  </si>
+  <si>
+    <t>R331</t>
+  </si>
+  <si>
+    <t>Resistor_SMD:R_0201_0603Metric_Pad0.64x0.40mm_HandSolder</t>
+  </si>
+  <si>
+    <t>R87</t>
+  </si>
+  <si>
+    <t>R88</t>
+  </si>
+  <si>
+    <t>R89</t>
+  </si>
+  <si>
+    <t>R90</t>
+  </si>
+  <si>
+    <t>R91</t>
+  </si>
+  <si>
+    <t>R92</t>
+  </si>
+  <si>
+    <t>R75</t>
+  </si>
+  <si>
+    <t>R76</t>
+  </si>
+  <si>
+    <t>R77</t>
+  </si>
+  <si>
+    <t>R78</t>
+  </si>
+  <si>
+    <t>R79</t>
+  </si>
+  <si>
+    <t>R80</t>
+  </si>
+  <si>
+    <t>R81</t>
+  </si>
+  <si>
+    <t>R82</t>
+  </si>
+  <si>
+    <t>R83</t>
+  </si>
+  <si>
+    <t>R84</t>
+  </si>
+  <si>
+    <t>R85</t>
+  </si>
+  <si>
+    <t>R86</t>
+  </si>
+  <si>
+    <t>R301</t>
+  </si>
+  <si>
+    <t>R302</t>
+  </si>
+  <si>
+    <t>R303</t>
+  </si>
+  <si>
+    <t>R304</t>
+  </si>
+  <si>
+    <t>R305</t>
+  </si>
+  <si>
+    <t>R306</t>
+  </si>
+  <si>
+    <t>R307</t>
+  </si>
+  <si>
+    <t>R308</t>
+  </si>
+  <si>
+    <t>R309</t>
+  </si>
+  <si>
+    <t>R310</t>
+  </si>
+  <si>
+    <t>R311</t>
+  </si>
+  <si>
+    <t>R312</t>
+  </si>
+  <si>
+    <t>R313</t>
+  </si>
+  <si>
+    <t>R314</t>
+  </si>
+  <si>
+    <t>R315</t>
+  </si>
+  <si>
+    <t>R316</t>
+  </si>
+  <si>
+    <t>R317</t>
+  </si>
+  <si>
+    <t>R318</t>
+  </si>
+  <si>
+    <t>CRCW040249R9FKED</t>
+  </si>
+  <si>
+    <t>47k</t>
+  </si>
+  <si>
+    <t>R321</t>
+  </si>
+  <si>
+    <t>R332</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>R27</t>
+  </si>
+  <si>
+    <t>RC0603JR-0747KL</t>
+  </si>
+  <si>
+    <t>Resistor_SMD:R_0402_1005Metric_Pad0.72x0.64mm_HandSolder</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>R28</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>R334</t>
+  </si>
+  <si>
+    <t>R319</t>
+  </si>
+  <si>
+    <t>R333</t>
+  </si>
+  <si>
+    <t>R320</t>
+  </si>
+  <si>
+    <t>CRCW0603100RFKEA</t>
+  </si>
+  <si>
+    <t>CRCW06031K00FKEA</t>
+  </si>
+  <si>
+    <t>Q301</t>
+  </si>
+  <si>
+    <t>Q302</t>
+  </si>
+  <si>
+    <t>D301</t>
+  </si>
+  <si>
+    <t>D302</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>OTW</t>
+  </si>
+  <si>
+    <t>FAULT</t>
+  </si>
+  <si>
+    <t>2N7002-7-F</t>
+  </si>
+  <si>
+    <t>LTST-C170KFKT</t>
+  </si>
+  <si>
+    <t>LED_0805</t>
+  </si>
+  <si>
+    <t>LTST-C170KRKT</t>
+  </si>
+  <si>
+    <t>Red 0805 LED</t>
+  </si>
+  <si>
+    <t>J301</t>
+  </si>
+  <si>
+    <t>I2S-IN</t>
+  </si>
+  <si>
+    <t>SBH11-PBPC-D10-ST-BK</t>
+  </si>
+  <si>
+    <t>eader (Shrouded), 2.54mm, 10x2, TH</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>U13</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>U310</t>
+  </si>
+  <si>
+    <t>U301</t>
+  </si>
+  <si>
+    <t>U302</t>
+  </si>
+  <si>
+    <t>U303</t>
+  </si>
+  <si>
+    <t>U304</t>
+  </si>
+  <si>
+    <t>U305</t>
+  </si>
+  <si>
+    <t>U306</t>
+  </si>
+  <si>
+    <t>U307</t>
+  </si>
+  <si>
+    <t>U308</t>
+  </si>
+  <si>
+    <t>U309</t>
+  </si>
+  <si>
+    <t>SN74LVC1G125DCKR</t>
+  </si>
+  <si>
+    <t>DCK0005A</t>
+  </si>
+  <si>
+    <t>Connector_IDC:IDC-Header_2x10_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>LED_SMD:LED_0805_2012Metric_Pad1.15x1.40mm_HandSolder</t>
+  </si>
+  <si>
+    <t>5-TSSOP</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD:SOT-353_SC-70-5_Handsoldering</t>
+  </si>
+  <si>
+    <t>R100</t>
+  </si>
+  <si>
+    <t>R408</t>
+  </si>
+  <si>
+    <t>CRCW060310R0JNEA</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C104</t>
+  </si>
+  <si>
+    <t>C106</t>
+  </si>
+  <si>
+    <t>C108</t>
+  </si>
+  <si>
+    <t>C405</t>
+  </si>
+  <si>
+    <t>C401</t>
+  </si>
+  <si>
+    <t>C403</t>
+  </si>
+  <si>
+    <t>GRM188R61A106ME69D</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_0201_0603Metric_Pad0.64x0.40mm_HandSolder</t>
+  </si>
+  <si>
+    <t>C105</t>
+  </si>
+  <si>
+    <t>C107</t>
+  </si>
+  <si>
+    <t>C109</t>
+  </si>
+  <si>
+    <t>C406</t>
+  </si>
+  <si>
+    <t>C402</t>
+  </si>
+  <si>
+    <t>C404</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_0402_1005Metric_Pad0.74x0.62mm_HandSolder</t>
+  </si>
+  <si>
+    <t>10k</t>
+  </si>
+  <si>
+    <t>R110</t>
+  </si>
+  <si>
+    <t>R111</t>
+  </si>
+  <si>
+    <t>R406</t>
+  </si>
+  <si>
+    <t>R407</t>
+  </si>
+  <si>
+    <t>R113</t>
+  </si>
+  <si>
+    <t>R114</t>
+  </si>
+  <si>
+    <t>R405</t>
+  </si>
+  <si>
+    <t>R404</t>
+  </si>
+  <si>
+    <t>ERJ-2RKF1002X</t>
+  </si>
+  <si>
+    <t>R112</t>
+  </si>
+  <si>
+    <t>R403</t>
+  </si>
+  <si>
+    <t>4.99k</t>
+  </si>
+  <si>
+    <t>R115</t>
+  </si>
+  <si>
+    <t>R117</t>
+  </si>
+  <si>
+    <t>R401</t>
+  </si>
+  <si>
+    <t>R402</t>
+  </si>
+  <si>
+    <t>CRCW04024K99FKED</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>J405</t>
+  </si>
+  <si>
+    <t>N2550-6002-RB</t>
+  </si>
+  <si>
+    <t>Header, 2.54mm, 25x2, TH</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_2x25_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>R101</t>
+  </si>
+  <si>
+    <t>R103</t>
+  </si>
+  <si>
+    <t>R105</t>
+  </si>
+  <si>
+    <t>R107</t>
+  </si>
+  <si>
+    <t>R409</t>
+  </si>
+  <si>
+    <t>R410</t>
+  </si>
+  <si>
+    <t>R411</t>
+  </si>
+  <si>
+    <t>R412</t>
+  </si>
+  <si>
+    <t>CRCW0603499RFKEA</t>
+  </si>
+  <si>
+    <t>C117</t>
+  </si>
+  <si>
+    <t>C121</t>
+  </si>
+  <si>
+    <t>C410</t>
+  </si>
+  <si>
+    <t>C411</t>
+  </si>
+  <si>
+    <t>GRM1555C1H102JA01D</t>
+  </si>
+  <si>
+    <t>1000pF</t>
+  </si>
+  <si>
+    <t>C122</t>
+  </si>
+  <si>
+    <t>C407</t>
+  </si>
+  <si>
+    <t>C1005X5R1A225K050BC</t>
+  </si>
+  <si>
+    <t>2.2uF</t>
+  </si>
+  <si>
+    <t>C128</t>
+  </si>
+  <si>
+    <t>C408</t>
+  </si>
+  <si>
+    <t>C130</t>
+  </si>
+  <si>
+    <t>JP100</t>
+  </si>
+  <si>
+    <t>JP101</t>
+  </si>
+  <si>
+    <t>JP102</t>
+  </si>
+  <si>
+    <t>JP103</t>
+  </si>
+  <si>
+    <t>JP401</t>
+  </si>
+  <si>
+    <t>JP402</t>
+  </si>
+  <si>
+    <t>JP403</t>
+  </si>
+  <si>
+    <t>JP404</t>
+  </si>
+  <si>
+    <t>PBC03SAAN</t>
+  </si>
+  <si>
+    <t>Connector_PinHeader_2.54mm:PinHeader_1x03_P2.54mm_Vertical_SMD_Pin1Left</t>
+  </si>
+  <si>
+    <t>C110</t>
+  </si>
+  <si>
+    <t>C119</t>
+  </si>
+  <si>
+    <t>C129</t>
+  </si>
+  <si>
+    <t>C134</t>
+  </si>
+  <si>
+    <t>C412</t>
+  </si>
+  <si>
+    <t>C414</t>
+  </si>
+  <si>
+    <t>C416</t>
+  </si>
+  <si>
+    <t>C418</t>
+  </si>
+  <si>
+    <t>GRM31CR71C106KAC7L</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_1206_3216Metric_Pad1.33x1.80mm_HandSolder</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>C118</t>
+  </si>
+  <si>
+    <t>C125</t>
+  </si>
+  <si>
+    <t>C131</t>
+  </si>
+  <si>
+    <t>C137</t>
+  </si>
+  <si>
+    <t>C413</t>
+  </si>
+  <si>
+    <t>C415</t>
+  </si>
+  <si>
+    <t>C417</t>
+  </si>
+  <si>
+    <t>C419</t>
+  </si>
+  <si>
+    <t>GRM1885C1H101JA01D</t>
+  </si>
+  <si>
+    <t>C101</t>
+  </si>
+  <si>
+    <t>C112</t>
+  </si>
+  <si>
+    <t>C124</t>
+  </si>
+  <si>
+    <t>C426</t>
+  </si>
+  <si>
+    <t>C428</t>
+  </si>
+  <si>
+    <t>C427</t>
+  </si>
+  <si>
+    <t>C0603C104K5RACTU</t>
+  </si>
+  <si>
+    <t>C132</t>
+  </si>
+  <si>
+    <t>C133</t>
+  </si>
+  <si>
+    <t>C429</t>
+  </si>
+  <si>
+    <t>C430</t>
+  </si>
+  <si>
+    <t>GRM188R71C105KA12D</t>
+  </si>
+  <si>
+    <t>0.047uF</t>
+  </si>
+  <si>
+    <t>C143</t>
+  </si>
+  <si>
+    <t>C431</t>
+  </si>
+  <si>
+    <t>GRM188R71H473KA61D</t>
+  </si>
+  <si>
+    <t>C144</t>
+  </si>
+  <si>
+    <t>C145</t>
+  </si>
+  <si>
+    <t>C432</t>
+  </si>
+  <si>
+    <t>C433</t>
+  </si>
+  <si>
+    <t>R119</t>
+  </si>
+  <si>
+    <t>22k</t>
+  </si>
+  <si>
+    <t>R417</t>
+  </si>
+  <si>
+    <t>RC0603FR-0722KL</t>
+  </si>
+  <si>
+    <t>30k</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>R418</t>
+  </si>
+  <si>
+    <t>RC0603FR-0730KL</t>
+  </si>
+  <si>
+    <t>L100</t>
+  </si>
+  <si>
+    <t>L401</t>
+  </si>
+  <si>
+    <t>GLFR1608T100M-LR</t>
+  </si>
+  <si>
+    <t>Inductor_SMD:L_0603_1608Metric_Pad1.05x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>C102</t>
+  </si>
+  <si>
+    <t>C103</t>
+  </si>
+  <si>
+    <t>C113</t>
+  </si>
+  <si>
+    <t>C114</t>
+  </si>
+  <si>
+    <t>C420</t>
+  </si>
+  <si>
+    <t>C421</t>
+  </si>
+  <si>
+    <t>C423</t>
+  </si>
+  <si>
+    <t>C424</t>
+  </si>
+  <si>
+    <t>GRM31MR71H105KA88L</t>
+  </si>
+  <si>
+    <t>1000uF</t>
+  </si>
+  <si>
+    <t>C422</t>
+  </si>
+  <si>
+    <t>C425</t>
+  </si>
+  <si>
+    <t>C100</t>
+  </si>
+  <si>
+    <t>C111</t>
+  </si>
+  <si>
+    <t>0.033uF</t>
+  </si>
+  <si>
+    <t>C120</t>
+  </si>
+  <si>
+    <t>C123</t>
+  </si>
+  <si>
+    <t>C138</t>
+  </si>
+  <si>
+    <t>C139</t>
+  </si>
+  <si>
+    <t>C434</t>
+  </si>
+  <si>
+    <t>C435</t>
+  </si>
+  <si>
+    <t>C444</t>
+  </si>
+  <si>
+    <t>C445</t>
+  </si>
+  <si>
+    <t>GRM188R71E333KA01D</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_0603_1608Metric_Pad1.08x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>C142</t>
+  </si>
+  <si>
+    <t>C446</t>
+  </si>
+  <si>
+    <t>L101</t>
+  </si>
+  <si>
+    <t>L102</t>
+  </si>
+  <si>
+    <t>L402</t>
+  </si>
+  <si>
+    <t>L403</t>
+  </si>
+  <si>
+    <t>UA8014-ALD</t>
+  </si>
+  <si>
+    <t>15.5x14mm</t>
+  </si>
+  <si>
+    <t>C115</t>
+  </si>
+  <si>
+    <t>C126</t>
+  </si>
+  <si>
+    <t>C135</t>
+  </si>
+  <si>
+    <t>C140</t>
+  </si>
+  <si>
+    <t>C436</t>
+  </si>
+  <si>
+    <t>C438</t>
+  </si>
+  <si>
+    <t>C440</t>
+  </si>
+  <si>
+    <t>C441</t>
+  </si>
+  <si>
+    <t>C3225X7R2A105K200AA</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_1210_3225Metric_Pad1.33x2.70mm_HandSolder</t>
+  </si>
+  <si>
+    <t>C116</t>
+  </si>
+  <si>
+    <t>0.01uF</t>
+  </si>
+  <si>
+    <t>C127</t>
+  </si>
+  <si>
+    <t>C136</t>
+  </si>
+  <si>
+    <t>C141</t>
+  </si>
+  <si>
+    <t>C437</t>
+  </si>
+  <si>
+    <t>C439</t>
+  </si>
+  <si>
+    <t>C442</t>
+  </si>
+  <si>
+    <t>C443</t>
+  </si>
+  <si>
+    <t>C0603C103K5RACTU</t>
+  </si>
+  <si>
+    <t>R104</t>
+  </si>
+  <si>
+    <t>R109</t>
+  </si>
+  <si>
+    <t>R118</t>
+  </si>
+  <si>
+    <t>R120</t>
+  </si>
+  <si>
+    <t>R422</t>
+  </si>
+  <si>
+    <t>R421</t>
+  </si>
+  <si>
+    <t>R420</t>
+  </si>
+  <si>
+    <t>R419</t>
+  </si>
+  <si>
+    <t>CRCW06033R30JNEA</t>
+  </si>
+  <si>
+    <t>SL+</t>
+  </si>
+  <si>
+    <t>SL-</t>
+  </si>
+  <si>
+    <t>SR+</t>
+  </si>
+  <si>
+    <t>SR-</t>
+  </si>
+  <si>
+    <t>J401</t>
+  </si>
+  <si>
+    <t>J402</t>
+  </si>
+  <si>
+    <t>J403</t>
+  </si>
+  <si>
+    <t>J404</t>
+  </si>
+  <si>
+    <t>63066-1</t>
+  </si>
+  <si>
+    <t>NewLibrary:630661MouserReel</t>
+  </si>
+  <si>
+    <t>U102</t>
+  </si>
+  <si>
+    <t>U103</t>
+  </si>
+  <si>
+    <t>U403</t>
+  </si>
+  <si>
+    <t>U404</t>
+  </si>
+  <si>
+    <t>U402</t>
+  </si>
+  <si>
+    <t>U101</t>
+  </si>
+  <si>
+    <t>DDV0044D_N</t>
+  </si>
+  <si>
+    <t>TPA3244DDWR</t>
+  </si>
+  <si>
+    <t>U100</t>
+  </si>
+  <si>
+    <t>U401</t>
+  </si>
+  <si>
+    <t>PCM5252RHBR</t>
+  </si>
+  <si>
+    <t>RHB0032E</t>
+  </si>
+  <si>
+    <t>Package_DFN_QFN:Texas_RHB0032E_VQFN-32-1EP_5x5mm_P0.5mm_EP3.45x3.45mm_ThermalVias</t>
+  </si>
+  <si>
+    <t>C502</t>
+  </si>
+  <si>
+    <t>C507</t>
+  </si>
+  <si>
+    <t>C504</t>
+  </si>
+  <si>
+    <t>C501</t>
+  </si>
+  <si>
+    <t>C503</t>
+  </si>
+  <si>
+    <t>C230</t>
+  </si>
+  <si>
+    <t>C505</t>
+  </si>
+  <si>
+    <t>C508</t>
+  </si>
+  <si>
+    <t>C506</t>
+  </si>
+  <si>
+    <t>C510</t>
+  </si>
+  <si>
+    <t>R200</t>
+  </si>
+  <si>
+    <t>R501</t>
+  </si>
+  <si>
+    <t>Resistor_SMD:R_0603_1608Metric_Pad0.98x0.95mm_HandSolder</t>
+  </si>
+  <si>
+    <t>R503</t>
+  </si>
+  <si>
+    <t>R504</t>
+  </si>
+  <si>
+    <t>R507</t>
+  </si>
+  <si>
+    <t>R508</t>
+  </si>
+  <si>
+    <t>R506</t>
+  </si>
+  <si>
+    <t>R502</t>
+  </si>
+  <si>
+    <t>R505</t>
+  </si>
+  <si>
+    <t>R509</t>
+  </si>
+  <si>
+    <t>R510</t>
+  </si>
+  <si>
+    <t>R511</t>
+  </si>
+  <si>
+    <t>R512</t>
+  </si>
+  <si>
+    <t>C221</t>
+  </si>
+  <si>
+    <t>C512</t>
+  </si>
+  <si>
+    <t>C513</t>
+  </si>
+  <si>
+    <t>C509</t>
+  </si>
+  <si>
+    <t>C511</t>
+  </si>
+  <si>
+    <t>C222</t>
+  </si>
+  <si>
+    <t>C228</t>
+  </si>
+  <si>
+    <t>JP200</t>
+  </si>
+  <si>
+    <t>JP201</t>
+  </si>
+  <si>
+    <t>JP202</t>
+  </si>
+  <si>
+    <t>JP203</t>
+  </si>
+  <si>
+    <t>JP501</t>
+  </si>
+  <si>
+    <t>JP502</t>
+  </si>
+  <si>
+    <t>JP503</t>
+  </si>
+  <si>
+    <t>JP504</t>
+  </si>
+  <si>
+    <t>C514</t>
+  </si>
+  <si>
+    <t>C515</t>
+  </si>
+  <si>
+    <t>C516</t>
+  </si>
+  <si>
+    <t>C517</t>
+  </si>
+  <si>
+    <t>C229</t>
+  </si>
+  <si>
+    <t>C234</t>
+  </si>
+  <si>
+    <t>R102</t>
+  </si>
+  <si>
+    <t>R106</t>
+  </si>
+  <si>
+    <t>R108</t>
+  </si>
+  <si>
+    <t>R116</t>
+  </si>
+  <si>
+    <t>R413</t>
+  </si>
+  <si>
+    <t>R414</t>
+  </si>
+  <si>
+    <t>R415</t>
+  </si>
+  <si>
+    <t>R416</t>
+  </si>
+  <si>
+    <t>R513</t>
+  </si>
+  <si>
+    <t>R514</t>
+  </si>
+  <si>
+    <t>R515</t>
+  </si>
+  <si>
+    <t>R516</t>
+  </si>
+  <si>
+    <t>C225</t>
+  </si>
+  <si>
+    <t>C231</t>
+  </si>
+  <si>
+    <t>C237</t>
+  </si>
+  <si>
+    <t>C518</t>
+  </si>
+  <si>
+    <t>C519</t>
+  </si>
+  <si>
+    <t>C520</t>
+  </si>
+  <si>
+    <t>C521</t>
+  </si>
+  <si>
+    <t>C224</t>
+  </si>
+  <si>
+    <t>C242</t>
+  </si>
+  <si>
+    <t>C538</t>
+  </si>
+  <si>
+    <t>C523</t>
+  </si>
+  <si>
+    <t>C522</t>
+  </si>
+  <si>
+    <t>C524</t>
+  </si>
+  <si>
+    <t>C232</t>
+  </si>
+  <si>
+    <t>C233</t>
+  </si>
+  <si>
+    <t>C525</t>
+  </si>
+  <si>
+    <t>C526</t>
+  </si>
+  <si>
+    <t>C527</t>
+  </si>
+  <si>
+    <t>C528</t>
+  </si>
+  <si>
+    <t>C530</t>
+  </si>
+  <si>
+    <t>C529</t>
+  </si>
+  <si>
+    <t>C531</t>
+  </si>
+  <si>
+    <t>C532</t>
+  </si>
+  <si>
+    <t>C200</t>
+  </si>
+  <si>
+    <t>L200</t>
+  </si>
+  <si>
+    <t>L501</t>
+  </si>
+  <si>
+    <t>C223</t>
+  </si>
+  <si>
+    <t>C238</t>
+  </si>
+  <si>
+    <t>C239</t>
+  </si>
+  <si>
+    <t>C534</t>
+  </si>
+  <si>
+    <t>C536</t>
+  </si>
+  <si>
+    <t>C537</t>
+  </si>
+  <si>
+    <t>C535</t>
+  </si>
+  <si>
+    <t>C533</t>
+  </si>
+  <si>
+    <t>C226</t>
+  </si>
+  <si>
+    <t>C235</t>
+  </si>
+  <si>
+    <t>C240</t>
+  </si>
+  <si>
+    <t>C539</t>
+  </si>
+  <si>
+    <t>C540</t>
+  </si>
+  <si>
+    <t>C541</t>
+  </si>
+  <si>
+    <t>C542</t>
+  </si>
+  <si>
+    <t>C227</t>
+  </si>
+  <si>
+    <t>C236</t>
+  </si>
+  <si>
+    <t>C241</t>
+  </si>
+  <si>
+    <t>C543</t>
+  </si>
+  <si>
+    <t>C544</t>
+  </si>
+  <si>
+    <t>R517</t>
+  </si>
+  <si>
+    <t>R519</t>
+  </si>
+  <si>
+    <t>R520</t>
+  </si>
+  <si>
+    <t>R521</t>
+  </si>
+  <si>
+    <t>R518</t>
+  </si>
+  <si>
+    <t>L201</t>
+  </si>
+  <si>
+    <t>L202</t>
+  </si>
+  <si>
+    <t>L502</t>
+  </si>
+  <si>
+    <t>L503</t>
+  </si>
+  <si>
+    <t>UP LEFT +</t>
+  </si>
+  <si>
+    <t>UPLEFT -</t>
+  </si>
+  <si>
+    <t>UP RIGHT +</t>
+  </si>
+  <si>
+    <t>UP RIGHT -</t>
+  </si>
+  <si>
+    <t>J501</t>
+  </si>
+  <si>
+    <t>J502</t>
+  </si>
+  <si>
+    <t>J503</t>
+  </si>
+  <si>
+    <t>J504</t>
+  </si>
+  <si>
+    <t>U502</t>
+  </si>
+  <si>
+    <t>U501</t>
+  </si>
+  <si>
+    <t>U200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -588,12 +2345,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -931,15 +2703,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A7B1A76-5DD3-4569-B12C-ED9F49EA38A1}">
-  <dimension ref="A1:T34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V176"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
-    <col min="6" max="6" width="25.75" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -965,17 +2737,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="12">
         <v>2</v>
       </c>
       <c r="E2" t="s">
@@ -1003,15 +2775,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="12"/>
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="12"/>
       <c r="E3">
         <v>402</v>
       </c>
@@ -1025,357 +2797,2856 @@
         <v>402</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="12"/>
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="12"/>
       <c r="E4">
         <v>402</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="12"/>
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="12"/>
       <c r="E5">
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="12"/>
       <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="12"/>
       <c r="E6">
         <v>402</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="12"/>
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="12"/>
       <c r="E7">
         <v>402</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="12"/>
       <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="12"/>
       <c r="E8">
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="12"/>
       <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="12"/>
       <c r="E9">
         <v>402</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="14" spans="1:20">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" t="s">
         <v>51</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H14" t="s">
         <v>25</v>
       </c>
-      <c r="I25" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" t="s">
-        <v>4</v>
-      </c>
-      <c r="M25" t="s">
+      <c r="I14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" t="s">
         <v>51</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="15" spans="1:20">
+      <c r="A15" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="3">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="3">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
-        <v>2</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="B15" s="12">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H15" t="s">
         <v>0</v>
       </c>
-      <c r="I26" s="3">
-        <v>1</v>
-      </c>
-      <c r="J26" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="3">
-        <v>2</v>
-      </c>
-      <c r="L26" t="s">
-        <v>2</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="I15" s="12">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="12">
+        <v>2</v>
+      </c>
+      <c r="L15" t="s">
+        <v>2</v>
+      </c>
+      <c r="M15" t="s">
         <v>52</v>
       </c>
-      <c r="O26" t="s">
+      <c r="O15" t="s">
         <v>0</v>
       </c>
-      <c r="P26" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>1</v>
-      </c>
-      <c r="R26" s="1">
-        <v>2</v>
-      </c>
-      <c r="S26" t="s">
-        <v>2</v>
-      </c>
-      <c r="T26" t="s">
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="1">
+        <v>2</v>
+      </c>
+      <c r="S15" t="s">
+        <v>2</v>
+      </c>
+      <c r="T15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="16" spans="1:20">
+      <c r="A16" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27">
+      <c r="D16" s="12"/>
+      <c r="E16">
         <v>603</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H16" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="3"/>
-      <c r="J27" t="s">
+      <c r="I16" s="12"/>
+      <c r="J16" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27">
+      <c r="K16" s="12"/>
+      <c r="L16">
         <v>402</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O16" t="s">
         <v>41</v>
       </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" t="s">
+      <c r="P16" s="1"/>
+      <c r="Q16" t="s">
         <v>29</v>
       </c>
-      <c r="R27" s="1"/>
-      <c r="S27">
+      <c r="R16" s="1"/>
+      <c r="S16">
         <v>402</v>
       </c>
-      <c r="T27" t="s">
+      <c r="T16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17">
+        <v>603</v>
+      </c>
+      <c r="H17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="12"/>
+      <c r="L17">
+        <v>402</v>
+      </c>
+      <c r="O17" t="s">
+        <v>42</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="Q17" t="s">
+        <v>30</v>
+      </c>
+      <c r="R17" s="1"/>
+      <c r="S17">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="B18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="O18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="Q18" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="B19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="O19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="Q19" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="S19">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="B20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="O20" t="s">
+        <v>45</v>
+      </c>
+      <c r="P20" s="1"/>
+      <c r="Q20" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" s="1"/>
+      <c r="S20">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="B21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="O21" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" t="s">
+        <v>34</v>
+      </c>
+      <c r="R21" s="1"/>
+      <c r="S21">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="B22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="O22" t="s">
+        <v>47</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" s="1"/>
+      <c r="S22">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="O23" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>36</v>
+      </c>
+      <c r="S23">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K28" t="s">
+        <v>4</v>
+      </c>
+      <c r="M28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="12">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="12">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>3</v>
+      </c>
+      <c r="L29" t="s">
+        <v>2</v>
+      </c>
+      <c r="M29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" t="s">
+        <v>277</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30">
+        <v>402</v>
+      </c>
+      <c r="H30" t="s">
+        <v>284</v>
+      </c>
+      <c r="J30" t="s">
+        <v>276</v>
+      </c>
+      <c r="L30">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" t="s">
+        <v>286</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" t="s">
+        <v>278</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" t="s">
+        <v>279</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
+      <c r="A33" t="s">
+        <v>288</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
+      <c r="A34" t="s">
+        <v>289</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" t="s">
+        <v>281</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
+      <c r="A35" t="s">
+        <v>290</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
+      <c r="A36" t="s">
+        <v>291</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" t="s">
+        <v>283</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
+      <c r="A43" t="s">
+        <v>414</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" t="s">
+        <v>414</v>
+      </c>
+      <c r="O43" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>4</v>
+      </c>
+      <c r="S43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="12">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="12">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>421</v>
+      </c>
+      <c r="G44" t="s">
+        <v>422</v>
+      </c>
+      <c r="N44" t="s">
+        <v>0</v>
+      </c>
+      <c r="O44" s="12">
+        <v>4</v>
+      </c>
+      <c r="P44" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="12">
+        <v>5</v>
+      </c>
+      <c r="R44" t="s">
+        <v>2</v>
+      </c>
+      <c r="S44" t="s">
+        <v>421</v>
+      </c>
+      <c r="V44" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
+      <c r="A45" t="s">
+        <v>415</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" t="s">
+        <v>418</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45">
+        <v>603</v>
+      </c>
+      <c r="N45" t="s">
+        <v>32</v>
+      </c>
+      <c r="O45" s="12"/>
+      <c r="P45" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q45" s="12"/>
+      <c r="R45">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
+      <c r="A46" t="s">
+        <v>416</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" t="s">
+        <v>419</v>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46">
+        <v>603</v>
+      </c>
+      <c r="N46" t="s">
+        <v>34</v>
+      </c>
+      <c r="O46" s="12"/>
+      <c r="P46" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q46" s="12"/>
+      <c r="R46">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
+      <c r="A47" t="s">
+        <v>417</v>
+      </c>
+      <c r="B47" s="12"/>
+      <c r="C47" t="s">
+        <v>420</v>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="N47" t="s">
+        <v>36</v>
+      </c>
+      <c r="O47" s="12"/>
+      <c r="P47" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q47" s="12"/>
+    </row>
+    <row r="48" spans="1:22">
+      <c r="B48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="O48" s="12"/>
+      <c r="Q48" s="12"/>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="B49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="O49" s="12"/>
+      <c r="Q49" s="12"/>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="B50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="O50" s="12"/>
+      <c r="Q50" s="12"/>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="B51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="O51" s="12"/>
+      <c r="Q51" s="12"/>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>4</v>
+      </c>
+      <c r="S54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="12">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="12">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2</v>
+      </c>
+      <c r="F55" t="s">
+        <v>55</v>
+      </c>
+      <c r="G55" t="s">
+        <v>429</v>
+      </c>
+      <c r="N55" t="s">
+        <v>0</v>
+      </c>
+      <c r="O55" s="12">
+        <v>4</v>
+      </c>
+      <c r="P55" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="12">
+        <v>5</v>
+      </c>
+      <c r="R55" t="s">
+        <v>2</v>
+      </c>
+      <c r="S55" t="s">
+        <v>55</v>
+      </c>
+      <c r="T55" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56" t="s">
+        <v>423</v>
+      </c>
+      <c r="B56" s="12"/>
+      <c r="C56" t="s">
+        <v>426</v>
+      </c>
+      <c r="D56" s="12"/>
+      <c r="E56">
+        <v>402</v>
+      </c>
+      <c r="N56" t="s">
+        <v>33</v>
+      </c>
+      <c r="O56" s="12"/>
+      <c r="P56" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q56" s="12"/>
+      <c r="R56">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="A57" t="s">
+        <v>424</v>
+      </c>
+      <c r="B57" s="12"/>
+      <c r="C57" t="s">
+        <v>427</v>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57">
+        <v>402</v>
+      </c>
+      <c r="N57" t="s">
+        <v>35</v>
+      </c>
+      <c r="O57" s="12"/>
+      <c r="P57" t="s">
+        <v>624</v>
+      </c>
+      <c r="Q57" s="12"/>
+      <c r="R57">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58" t="s">
+        <v>425</v>
+      </c>
+      <c r="B58" s="12"/>
+      <c r="C58" t="s">
+        <v>428</v>
+      </c>
+      <c r="D58" s="12"/>
+      <c r="E58">
+        <v>402</v>
+      </c>
+      <c r="N58" t="s">
+        <v>14</v>
+      </c>
+      <c r="O58" s="12"/>
+      <c r="P58" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q58" s="12"/>
+      <c r="R58">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59" t="s">
+        <v>474</v>
+      </c>
+      <c r="B59" s="12"/>
+      <c r="C59" t="s">
+        <v>473</v>
+      </c>
+      <c r="D59" s="12"/>
+      <c r="N59" t="s">
+        <v>627</v>
+      </c>
+      <c r="O59" s="12"/>
+      <c r="P59" t="s">
+        <v>623</v>
+      </c>
+      <c r="Q59" s="12"/>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="B60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="O60" s="12"/>
+      <c r="Q60" s="12"/>
+    </row>
+    <row r="61" spans="1:20">
+      <c r="B61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="Q61" s="12"/>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="B62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="Q62" s="12"/>
+    </row>
+    <row r="66" spans="1:21">
+      <c r="A66" t="s">
+        <v>467</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" t="s">
+        <v>467</v>
+      </c>
+      <c r="O66" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>4</v>
+      </c>
+      <c r="S66" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
+      <c r="A67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="12">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="12">
+        <v>4</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>466</v>
+      </c>
+      <c r="H67" t="s">
+        <v>429</v>
+      </c>
+      <c r="N67" t="s">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12">
+        <v>4</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="12">
+        <v>5</v>
+      </c>
+      <c r="R67" t="s">
+        <v>2</v>
+      </c>
+      <c r="S67" t="s">
+        <v>466</v>
+      </c>
+      <c r="U67" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
+      <c r="A68" t="s">
+        <v>462</v>
+      </c>
+      <c r="B68" s="12"/>
+      <c r="C68" t="s">
+        <v>464</v>
+      </c>
+      <c r="D68" s="12"/>
+      <c r="E68">
+        <v>402</v>
+      </c>
+      <c r="N68" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28">
+      <c r="O68" s="12"/>
+      <c r="P68" t="s">
+        <v>629</v>
+      </c>
+      <c r="Q68" s="12"/>
+      <c r="R68">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
+      <c r="A69" t="s">
+        <v>463</v>
+      </c>
+      <c r="B69" s="12"/>
+      <c r="C69" t="s">
+        <v>465</v>
+      </c>
+      <c r="D69" s="12"/>
+      <c r="E69">
+        <v>402</v>
+      </c>
+      <c r="N69" t="s">
+        <v>646</v>
+      </c>
+      <c r="O69" s="12"/>
+      <c r="P69" t="s">
+        <v>631</v>
+      </c>
+      <c r="Q69" s="12"/>
+      <c r="R69">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
+      <c r="B70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="Q70" s="6"/>
+    </row>
+    <row r="71" spans="1:21">
+      <c r="B71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="Q71" s="6"/>
+    </row>
+    <row r="72" spans="1:21">
+      <c r="A72" t="s">
+        <v>471</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" t="s">
+        <v>471</v>
+      </c>
+      <c r="O72" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" s="12">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="12">
+        <v>4</v>
+      </c>
+      <c r="E73" t="s">
+        <v>2</v>
+      </c>
+      <c r="F73" t="s">
+        <v>470</v>
+      </c>
+      <c r="N73" t="s">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12">
+        <v>4</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="12">
+        <v>5</v>
+      </c>
+      <c r="R73" t="s">
+        <v>2</v>
+      </c>
+      <c r="S73" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
+      <c r="A74" t="s">
+        <v>468</v>
+      </c>
+      <c r="B74" s="12"/>
+      <c r="C74" t="s">
+        <v>469</v>
+      </c>
+      <c r="D74" s="12"/>
+      <c r="E74">
+        <v>402</v>
+      </c>
+      <c r="N74" t="s">
+        <v>651</v>
+      </c>
+      <c r="O74" s="12"/>
+      <c r="P74" t="s">
+        <v>649</v>
+      </c>
+      <c r="Q74" s="12"/>
+      <c r="R74">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
+      <c r="A75" t="s">
+        <v>472</v>
+      </c>
+      <c r="B75" s="6"/>
+      <c r="C75" t="s">
+        <v>473</v>
+      </c>
+      <c r="D75" s="6"/>
+      <c r="N75" t="s">
+        <v>652</v>
+      </c>
+      <c r="O75" s="6"/>
+      <c r="P75" t="s">
+        <v>650</v>
+      </c>
+      <c r="Q75" s="6"/>
+    </row>
+    <row r="76" spans="1:21">
+      <c r="B76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="O76" s="6"/>
+      <c r="Q76" s="6"/>
+    </row>
+    <row r="78" spans="1:21">
+      <c r="A78" t="s">
+        <v>471</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" t="s">
+        <v>471</v>
+      </c>
+      <c r="O78" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>4</v>
+      </c>
+      <c r="S78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
+      <c r="A79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="12">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="12">
+        <v>4</v>
+      </c>
+      <c r="E79" t="s">
+        <v>2</v>
+      </c>
+      <c r="F79" t="s">
+        <v>470</v>
+      </c>
+      <c r="N79" t="s">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12">
+        <v>4</v>
+      </c>
+      <c r="P79" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="12">
+        <v>5</v>
+      </c>
+      <c r="R79" t="s">
+        <v>2</v>
+      </c>
+      <c r="S79" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
+      <c r="A80" t="s">
+        <v>468</v>
+      </c>
+      <c r="B80" s="12"/>
+      <c r="C80" t="s">
+        <v>469</v>
+      </c>
+      <c r="D80" s="12"/>
+      <c r="E80">
+        <v>402</v>
+      </c>
+      <c r="N80" t="s">
+        <v>468</v>
+      </c>
+      <c r="O80" s="12"/>
+      <c r="P80" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q80" s="12"/>
+      <c r="R80">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19">
+      <c r="A83" t="s">
+        <v>414</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" t="s">
+        <v>51</v>
+      </c>
+      <c r="N83" t="s">
+        <v>414</v>
+      </c>
+      <c r="O83" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>4</v>
+      </c>
+      <c r="S83" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19">
+      <c r="A84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" s="12">
+        <v>3</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="12">
+        <v>4</v>
+      </c>
+      <c r="E84" t="s">
+        <v>2</v>
+      </c>
+      <c r="F84" t="s">
+        <v>493</v>
+      </c>
+      <c r="N84" t="s">
+        <v>0</v>
+      </c>
+      <c r="O84" s="12">
+        <v>4</v>
+      </c>
+      <c r="P84" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q84" s="12">
+        <v>5</v>
+      </c>
+      <c r="R84" t="s">
+        <v>2</v>
+      </c>
+      <c r="S84" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19">
+      <c r="A85" t="s">
+        <v>485</v>
+      </c>
+      <c r="B85" s="12"/>
+      <c r="C85" t="s">
+        <v>489</v>
+      </c>
+      <c r="D85" s="12"/>
+      <c r="E85">
+        <v>1206</v>
+      </c>
+      <c r="N85" t="s">
+        <v>15</v>
+      </c>
+      <c r="O85" s="12"/>
+      <c r="P85" t="s">
+        <v>647</v>
+      </c>
+      <c r="Q85" s="12"/>
+      <c r="R85">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19">
+      <c r="A86" t="s">
+        <v>486</v>
+      </c>
+      <c r="B86" s="12"/>
+      <c r="C86" t="s">
+        <v>490</v>
+      </c>
+      <c r="D86" s="12"/>
+      <c r="E86">
+        <v>1206</v>
+      </c>
+      <c r="F86" t="s">
+        <v>494</v>
+      </c>
+      <c r="N86" t="s">
+        <v>26</v>
+      </c>
+      <c r="O86" s="12"/>
+      <c r="P86" t="s">
+        <v>648</v>
+      </c>
+      <c r="Q86" s="12"/>
+      <c r="R86">
+        <v>1206</v>
+      </c>
+      <c r="S86" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19">
+      <c r="A87" t="s">
+        <v>487</v>
+      </c>
+      <c r="B87" s="12"/>
+      <c r="C87" t="s">
+        <v>491</v>
+      </c>
+      <c r="D87" s="12"/>
+      <c r="N87" t="s">
+        <v>665</v>
+      </c>
+      <c r="O87" s="12"/>
+      <c r="P87" t="s">
+        <v>661</v>
+      </c>
+      <c r="Q87" s="12"/>
+    </row>
+    <row r="88" spans="1:19">
+      <c r="A88" t="s">
+        <v>488</v>
+      </c>
+      <c r="B88" s="12"/>
+      <c r="C88" t="s">
+        <v>492</v>
+      </c>
+      <c r="D88" s="12"/>
+      <c r="N88" t="s">
+        <v>666</v>
+      </c>
+      <c r="O88" s="12"/>
+      <c r="P88" t="s">
+        <v>662</v>
+      </c>
+      <c r="Q88" s="12"/>
+    </row>
+    <row r="89" spans="1:19">
+      <c r="B89" s="12"/>
+      <c r="D89" s="12"/>
+      <c r="O89" s="12"/>
+      <c r="Q89" s="12"/>
+    </row>
+    <row r="90" spans="1:19">
+      <c r="B90" s="12"/>
+      <c r="D90" s="12"/>
+      <c r="O90" s="12"/>
+      <c r="Q90" s="12"/>
+    </row>
+    <row r="91" spans="1:19">
+      <c r="B91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="O91" s="12"/>
+      <c r="Q91" s="12"/>
+    </row>
+    <row r="94" spans="1:19">
+      <c r="A94" t="s">
+        <v>495</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" t="s">
+        <v>51</v>
+      </c>
+      <c r="N94" t="s">
+        <v>495</v>
+      </c>
+      <c r="O94" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19">
+      <c r="A95" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="12">
+        <v>3</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" s="12">
+        <v>4</v>
+      </c>
+      <c r="E95" t="s">
+        <v>2</v>
+      </c>
+      <c r="F95" t="s">
+        <v>504</v>
+      </c>
+      <c r="N95" t="s">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12">
+        <v>4</v>
+      </c>
+      <c r="P95" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="12">
+        <v>5</v>
+      </c>
+      <c r="R95" t="s">
+        <v>2</v>
+      </c>
+      <c r="S95" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19">
+      <c r="A96" t="s">
+        <v>496</v>
+      </c>
+      <c r="B96" s="12"/>
+      <c r="C96" t="s">
+        <v>500</v>
+      </c>
+      <c r="D96" s="12"/>
+      <c r="E96">
         <v>603</v>
       </c>
-      <c r="H28" t="s">
-        <v>38</v>
-      </c>
-      <c r="I28" s="3"/>
-      <c r="J28" t="s">
+      <c r="N96" t="s">
+        <v>23</v>
+      </c>
+      <c r="O96" s="12"/>
+      <c r="P96" t="s">
+        <v>663</v>
+      </c>
+      <c r="Q96" s="12"/>
+      <c r="R96">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19">
+      <c r="A97" t="s">
+        <v>497</v>
+      </c>
+      <c r="B97" s="12"/>
+      <c r="C97" t="s">
+        <v>501</v>
+      </c>
+      <c r="D97" s="12"/>
+      <c r="E97">
+        <v>603</v>
+      </c>
+      <c r="F97" t="s">
+        <v>422</v>
+      </c>
+      <c r="N97" t="s">
+        <v>679</v>
+      </c>
+      <c r="O97" s="12"/>
+      <c r="P97" t="s">
+        <v>664</v>
+      </c>
+      <c r="Q97" s="12"/>
+      <c r="R97">
+        <v>603</v>
+      </c>
+      <c r="S97" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19">
+      <c r="A98" t="s">
+        <v>498</v>
+      </c>
+      <c r="B98" s="12"/>
+      <c r="C98" t="s">
+        <v>502</v>
+      </c>
+      <c r="D98" s="12"/>
+      <c r="N98" t="s">
+        <v>680</v>
+      </c>
+      <c r="O98" s="12"/>
+      <c r="P98" t="s">
+        <v>682</v>
+      </c>
+      <c r="Q98" s="12"/>
+    </row>
+    <row r="99" spans="1:19">
+      <c r="A99" t="s">
+        <v>499</v>
+      </c>
+      <c r="B99" s="12"/>
+      <c r="C99" t="s">
+        <v>503</v>
+      </c>
+      <c r="D99" s="12"/>
+      <c r="N99" t="s">
+        <v>681</v>
+      </c>
+      <c r="O99" s="12"/>
+      <c r="P99" t="s">
+        <v>683</v>
+      </c>
+      <c r="Q99" s="12"/>
+    </row>
+    <row r="100" spans="1:19">
+      <c r="B100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="O100" s="12"/>
+      <c r="Q100" s="12"/>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="B101" s="12"/>
+      <c r="D101" s="12"/>
+      <c r="O101" s="12"/>
+      <c r="Q101" s="12"/>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="B102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="O102" s="12"/>
+      <c r="Q102" s="12"/>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" t="s">
+        <v>4</v>
+      </c>
+      <c r="F104" t="s">
+        <v>51</v>
+      </c>
+      <c r="N104" t="s">
+        <v>3</v>
+      </c>
+      <c r="O104" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>4</v>
+      </c>
+      <c r="S104" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="12">
+        <v>3</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1</v>
+      </c>
+      <c r="D105" s="12">
+        <v>4</v>
+      </c>
+      <c r="E105" t="s">
+        <v>2</v>
+      </c>
+      <c r="F105" t="s">
+        <v>511</v>
+      </c>
+      <c r="N105" t="s">
+        <v>0</v>
+      </c>
+      <c r="O105" s="12">
+        <v>4</v>
+      </c>
+      <c r="P105" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q105" s="12">
+        <v>5</v>
+      </c>
+      <c r="R105" t="s">
+        <v>2</v>
+      </c>
+      <c r="S105" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" t="s">
+        <v>505</v>
+      </c>
+      <c r="B106" s="12"/>
+      <c r="C106" t="s">
+        <v>508</v>
+      </c>
+      <c r="D106" s="12"/>
+      <c r="E106">
+        <v>603</v>
+      </c>
+      <c r="N106" t="s">
+        <v>29</v>
+      </c>
+      <c r="O106" s="12"/>
+      <c r="P106" t="s">
+        <v>684</v>
+      </c>
+      <c r="Q106" s="12"/>
+      <c r="R106">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" t="s">
+        <v>506</v>
+      </c>
+      <c r="B107" s="12"/>
+      <c r="C107" t="s">
+        <v>509</v>
+      </c>
+      <c r="D107" s="12"/>
+      <c r="E107">
+        <v>603</v>
+      </c>
+      <c r="F107" t="s">
+        <v>561</v>
+      </c>
+      <c r="N107" t="s">
+        <v>17</v>
+      </c>
+      <c r="O107" s="12"/>
+      <c r="P107" t="s">
+        <v>685</v>
+      </c>
+      <c r="Q107" s="12"/>
+      <c r="R107">
+        <v>603</v>
+      </c>
+      <c r="S107" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" t="s">
+        <v>507</v>
+      </c>
+      <c r="B108" s="12"/>
+      <c r="C108" t="s">
+        <v>510</v>
+      </c>
+      <c r="D108" s="12"/>
+      <c r="N108" t="s">
+        <v>686</v>
+      </c>
+      <c r="O108" s="12"/>
+      <c r="P108" t="s">
+        <v>690</v>
+      </c>
+      <c r="Q108" s="12"/>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" t="s">
+        <v>562</v>
+      </c>
+      <c r="B109" s="12"/>
+      <c r="C109" t="s">
+        <v>563</v>
+      </c>
+      <c r="D109" s="12"/>
+      <c r="N109" t="s">
+        <v>687</v>
+      </c>
+      <c r="O109" s="12"/>
+      <c r="P109" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q109" s="12"/>
+    </row>
+    <row r="110" spans="1:19">
+      <c r="B110" s="12"/>
+      <c r="D110" s="12"/>
+      <c r="O110" s="12"/>
+      <c r="Q110" s="12"/>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="B111" s="12"/>
+      <c r="D111" s="12"/>
+      <c r="O111" s="12"/>
+      <c r="Q111" s="12"/>
+    </row>
+    <row r="112" spans="1:19">
+      <c r="B112" s="12"/>
+      <c r="D112" s="12"/>
+      <c r="O112" s="12"/>
+      <c r="Q112" s="12"/>
+    </row>
+    <row r="114" spans="1:19">
+      <c r="A114" t="s">
+        <v>12</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" t="s">
+        <v>51</v>
+      </c>
+      <c r="N114" t="s">
+        <v>12</v>
+      </c>
+      <c r="O114" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>4</v>
+      </c>
+      <c r="S114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19">
+      <c r="A115" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" s="12">
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1</v>
+      </c>
+      <c r="D115" s="12">
+        <v>4</v>
+      </c>
+      <c r="E115" t="s">
+        <v>2</v>
+      </c>
+      <c r="F115" t="s">
+        <v>516</v>
+      </c>
+      <c r="N115" t="s">
+        <v>0</v>
+      </c>
+      <c r="O115" s="12">
+        <v>4</v>
+      </c>
+      <c r="P115" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q115" s="12">
+        <v>5</v>
+      </c>
+      <c r="R115" t="s">
+        <v>2</v>
+      </c>
+      <c r="S115" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19">
+      <c r="A116" t="s">
+        <v>512</v>
+      </c>
+      <c r="B116" s="12"/>
+      <c r="C116" t="s">
+        <v>514</v>
+      </c>
+      <c r="D116" s="12"/>
+      <c r="E116">
+        <v>603</v>
+      </c>
+      <c r="F116" t="s">
+        <v>422</v>
+      </c>
+      <c r="N116" t="s">
+        <v>692</v>
+      </c>
+      <c r="O116" s="12"/>
+      <c r="P116" t="s">
+        <v>691</v>
+      </c>
+      <c r="Q116" s="12"/>
+      <c r="R116">
+        <v>603</v>
+      </c>
+      <c r="S116" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19">
+      <c r="A117" t="s">
+        <v>513</v>
+      </c>
+      <c r="B117" s="6"/>
+      <c r="C117" t="s">
+        <v>515</v>
+      </c>
+      <c r="D117" s="6"/>
+      <c r="N117" t="s">
+        <v>693</v>
+      </c>
+      <c r="O117" s="6"/>
+      <c r="P117" t="s">
+        <v>694</v>
+      </c>
+      <c r="Q117" s="6"/>
+    </row>
+    <row r="120" spans="1:19">
+      <c r="A120" t="s">
+        <v>517</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" t="s">
+        <v>4</v>
+      </c>
+      <c r="F120" t="s">
+        <v>51</v>
+      </c>
+      <c r="N120" t="s">
+        <v>517</v>
+      </c>
+      <c r="O120" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>4</v>
+      </c>
+      <c r="S120" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19">
+      <c r="A121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B121" s="12">
+        <v>3</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1</v>
+      </c>
+      <c r="D121" s="12">
+        <v>4</v>
+      </c>
+      <c r="E121" t="s">
+        <v>2</v>
+      </c>
+      <c r="F121" t="s">
+        <v>520</v>
+      </c>
+      <c r="N121" t="s">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12">
+        <v>4</v>
+      </c>
+      <c r="P121" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q121" s="12">
+        <v>5</v>
+      </c>
+      <c r="R121" t="s">
+        <v>2</v>
+      </c>
+      <c r="S121" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19">
+      <c r="A122" t="s">
+        <v>518</v>
+      </c>
+      <c r="B122" s="12"/>
+      <c r="C122" t="s">
+        <v>519</v>
+      </c>
+      <c r="D122" s="12"/>
+      <c r="E122">
+        <v>603</v>
+      </c>
+      <c r="F122" t="s">
+        <v>422</v>
+      </c>
+      <c r="N122" t="s">
+        <v>543</v>
+      </c>
+      <c r="O122" s="12"/>
+      <c r="P122" t="s">
+        <v>695</v>
+      </c>
+      <c r="Q122" s="12"/>
+      <c r="R122">
+        <v>603</v>
+      </c>
+      <c r="S122" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19">
+      <c r="A124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F124" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19">
+      <c r="A125" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" s="12">
+        <v>3</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1</v>
+      </c>
+      <c r="D125" s="12">
+        <v>4</v>
+      </c>
+      <c r="E125" t="s">
+        <v>2</v>
+      </c>
+      <c r="F125" t="s">
+        <v>55</v>
+      </c>
+      <c r="O125" s="12"/>
+      <c r="Q125" s="12"/>
+    </row>
+    <row r="126" spans="1:19">
+      <c r="A126" t="s">
+        <v>521</v>
+      </c>
+      <c r="B126" s="12"/>
+      <c r="C126" t="s">
+        <v>523</v>
+      </c>
+      <c r="D126" s="12"/>
+      <c r="E126">
+        <v>402</v>
+      </c>
+      <c r="F126" t="s">
+        <v>429</v>
+      </c>
+      <c r="O126" s="12"/>
+      <c r="Q126" s="12"/>
+    </row>
+    <row r="127" spans="1:19">
+      <c r="A127" t="s">
+        <v>522</v>
+      </c>
+      <c r="B127" s="6"/>
+      <c r="C127" t="s">
+        <v>524</v>
+      </c>
+      <c r="D127" s="6"/>
+      <c r="E127">
+        <v>402</v>
+      </c>
+      <c r="O127" s="6"/>
+      <c r="Q127" s="6"/>
+    </row>
+    <row r="130" spans="1:19">
+      <c r="A130" t="s">
+        <v>12</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4</v>
+      </c>
+      <c r="D130" t="s">
+        <v>4</v>
+      </c>
+      <c r="F130" t="s">
+        <v>51</v>
+      </c>
+      <c r="N130" t="s">
+        <v>12</v>
+      </c>
+      <c r="O130" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>4</v>
+      </c>
+      <c r="S130" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19">
+      <c r="A131" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" s="12">
+        <v>3</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1</v>
+      </c>
+      <c r="D131" s="12">
+        <v>4</v>
+      </c>
+      <c r="E131" t="s">
+        <v>2</v>
+      </c>
+      <c r="F131" t="s">
+        <v>545</v>
+      </c>
+      <c r="N131" t="s">
+        <v>0</v>
+      </c>
+      <c r="O131" s="12">
+        <v>4</v>
+      </c>
+      <c r="P131" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q131" s="12">
+        <v>5</v>
+      </c>
+      <c r="R131" t="s">
+        <v>2</v>
+      </c>
+      <c r="S131" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19">
+      <c r="A132" t="s">
+        <v>537</v>
+      </c>
+      <c r="B132" s="12"/>
+      <c r="C132" t="s">
+        <v>541</v>
+      </c>
+      <c r="D132" s="12"/>
+      <c r="E132">
+        <v>1206</v>
+      </c>
+      <c r="N132" t="s">
+        <v>30</v>
+      </c>
+      <c r="O132" s="12"/>
+      <c r="P132" t="s">
+        <v>696</v>
+      </c>
+      <c r="Q132" s="12"/>
+      <c r="R132">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19">
+      <c r="A133" t="s">
+        <v>538</v>
+      </c>
+      <c r="B133" s="12"/>
+      <c r="C133" t="s">
+        <v>542</v>
+      </c>
+      <c r="D133" s="12"/>
+      <c r="E133">
+        <v>1206</v>
+      </c>
+      <c r="F133" t="s">
+        <v>494</v>
+      </c>
+      <c r="N133" t="s">
+        <v>31</v>
+      </c>
+      <c r="O133" s="12"/>
+      <c r="P133" t="s">
+        <v>697</v>
+      </c>
+      <c r="Q133" s="12"/>
+      <c r="R133">
+        <v>1206</v>
+      </c>
+      <c r="S133" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19">
+      <c r="A134" t="s">
+        <v>539</v>
+      </c>
+      <c r="B134" s="12"/>
+      <c r="C134" t="s">
+        <v>543</v>
+      </c>
+      <c r="D134" s="12"/>
+      <c r="N134" t="s">
+        <v>18</v>
+      </c>
+      <c r="O134" s="12"/>
+      <c r="P134" t="s">
+        <v>698</v>
+      </c>
+      <c r="Q134" s="12"/>
+    </row>
+    <row r="135" spans="1:19">
+      <c r="A135" t="s">
+        <v>540</v>
+      </c>
+      <c r="B135" s="12"/>
+      <c r="C135" t="s">
+        <v>544</v>
+      </c>
+      <c r="D135" s="12"/>
+      <c r="N135" t="s">
+        <v>19</v>
+      </c>
+      <c r="O135" s="12"/>
+      <c r="P135" t="s">
+        <v>700</v>
+      </c>
+      <c r="Q135" s="12"/>
+    </row>
+    <row r="136" spans="1:19">
+      <c r="B136" s="12"/>
+      <c r="D136" s="12"/>
+      <c r="O136" s="12"/>
+      <c r="Q136" s="12"/>
+    </row>
+    <row r="137" spans="1:19">
+      <c r="B137" s="12"/>
+      <c r="D137" s="12"/>
+      <c r="O137" s="12"/>
+      <c r="Q137" s="12"/>
+    </row>
+    <row r="138" spans="1:19">
+      <c r="B138" s="12"/>
+      <c r="D138" s="12"/>
+      <c r="O138" s="12"/>
+      <c r="Q138" s="12"/>
+    </row>
+    <row r="140" spans="1:19">
+      <c r="A140" t="s">
+        <v>546</v>
+      </c>
+      <c r="B140" t="s">
+        <v>4</v>
+      </c>
+      <c r="D140" t="s">
+        <v>4</v>
+      </c>
+      <c r="F140" t="s">
+        <v>51</v>
+      </c>
+      <c r="N140" t="s">
+        <v>546</v>
+      </c>
+      <c r="O140" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>4</v>
+      </c>
+      <c r="S140" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19">
+      <c r="A141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B141" s="12">
+        <v>3</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1</v>
+      </c>
+      <c r="D141" s="12">
+        <v>4</v>
+      </c>
+      <c r="E141" t="s">
+        <v>2</v>
+      </c>
+      <c r="F141" t="s">
+        <v>545</v>
+      </c>
+      <c r="N141" t="s">
+        <v>0</v>
+      </c>
+      <c r="O141" s="12">
+        <v>4</v>
+      </c>
+      <c r="P141" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q141" s="12">
+        <v>5</v>
+      </c>
+      <c r="R141" t="s">
+        <v>2</v>
+      </c>
+      <c r="S141" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19">
+      <c r="A142" t="s">
+        <v>549</v>
+      </c>
+      <c r="B142" s="12"/>
+      <c r="C142" t="s">
+        <v>547</v>
+      </c>
+      <c r="D142" s="12"/>
+      <c r="E142">
+        <v>1206</v>
+      </c>
+      <c r="F142" t="s">
+        <v>494</v>
+      </c>
+      <c r="N142" t="s">
+        <v>702</v>
+      </c>
+      <c r="O142" s="12"/>
+      <c r="P142" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q142" s="12"/>
+      <c r="R142">
+        <v>1206</v>
+      </c>
+      <c r="S142" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19">
+      <c r="A143" t="s">
+        <v>550</v>
+      </c>
+      <c r="B143" s="6"/>
+      <c r="C143" t="s">
+        <v>548</v>
+      </c>
+      <c r="D143" s="6"/>
+      <c r="E143">
+        <v>1206</v>
+      </c>
+      <c r="N143" t="s">
+        <v>16</v>
+      </c>
+      <c r="O143" s="6"/>
+      <c r="P143" t="s">
+        <v>701</v>
+      </c>
+      <c r="Q143" s="6"/>
+      <c r="R143">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19">
+      <c r="A146" t="s">
+        <v>551</v>
+      </c>
+      <c r="B146" t="s">
+        <v>4</v>
+      </c>
+      <c r="D146" t="s">
+        <v>4</v>
+      </c>
+      <c r="F146" t="s">
+        <v>51</v>
+      </c>
+      <c r="N146" t="s">
+        <v>551</v>
+      </c>
+      <c r="O146" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>4</v>
+      </c>
+      <c r="S146" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19">
+      <c r="A147" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" s="12">
+        <v>3</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1</v>
+      </c>
+      <c r="D147" s="12">
+        <v>4</v>
+      </c>
+      <c r="E147" t="s">
+        <v>2</v>
+      </c>
+      <c r="F147" t="s">
+        <v>560</v>
+      </c>
+      <c r="N147" t="s">
+        <v>0</v>
+      </c>
+      <c r="O147" s="12">
+        <v>4</v>
+      </c>
+      <c r="P147" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q147" s="12">
+        <v>5</v>
+      </c>
+      <c r="R147" t="s">
+        <v>2</v>
+      </c>
+      <c r="S147" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19">
+      <c r="A148" t="s">
+        <v>552</v>
+      </c>
+      <c r="B148" s="12"/>
+      <c r="C148" t="s">
+        <v>556</v>
+      </c>
+      <c r="D148" s="12"/>
+      <c r="E148">
+        <v>603</v>
+      </c>
+      <c r="N148" t="s">
         <v>27</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28">
-        <v>402</v>
-      </c>
-      <c r="O28" t="s">
-        <v>42</v>
-      </c>
-      <c r="P28" s="1"/>
-      <c r="Q28" t="s">
-        <v>30</v>
-      </c>
-      <c r="R28" s="1"/>
-      <c r="S28">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="O29" t="s">
-        <v>43</v>
-      </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" t="s">
-        <v>31</v>
-      </c>
-      <c r="R29" s="1"/>
-      <c r="S29">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="O30" t="s">
-        <v>44</v>
-      </c>
-      <c r="P30" s="1"/>
-      <c r="Q30" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" s="1"/>
-      <c r="S30">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="O31" t="s">
-        <v>45</v>
-      </c>
-      <c r="P31" s="1"/>
-      <c r="Q31" t="s">
-        <v>33</v>
-      </c>
-      <c r="R31" s="1"/>
-      <c r="S31">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="B32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="O32" t="s">
-        <v>46</v>
-      </c>
-      <c r="P32" s="1"/>
-      <c r="Q32" t="s">
-        <v>34</v>
-      </c>
-      <c r="R32" s="1"/>
-      <c r="S32">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="O33" t="s">
-        <v>47</v>
-      </c>
-      <c r="P33" s="1"/>
-      <c r="Q33" t="s">
-        <v>35</v>
-      </c>
-      <c r="R33" s="1"/>
-      <c r="S33">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="O34" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>36</v>
-      </c>
+      <c r="O148" s="12"/>
+      <c r="P148" t="s">
+        <v>712</v>
+      </c>
+      <c r="Q148" s="12"/>
+      <c r="R148">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19">
+      <c r="A149" t="s">
+        <v>553</v>
+      </c>
+      <c r="B149" s="12"/>
+      <c r="C149" t="s">
+        <v>557</v>
+      </c>
+      <c r="D149" s="12"/>
+      <c r="E149">
+        <v>603</v>
+      </c>
+      <c r="F149" t="s">
+        <v>561</v>
+      </c>
+      <c r="N149" t="s">
+        <v>705</v>
+      </c>
+      <c r="O149" s="12"/>
+      <c r="P149" t="s">
+        <v>708</v>
+      </c>
+      <c r="Q149" s="12"/>
+      <c r="R149">
+        <v>603</v>
+      </c>
+      <c r="S149" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19">
+      <c r="A150" t="s">
+        <v>554</v>
+      </c>
+      <c r="B150" s="12"/>
+      <c r="C150" t="s">
+        <v>558</v>
+      </c>
+      <c r="D150" s="12"/>
+      <c r="N150" t="s">
+        <v>706</v>
+      </c>
+      <c r="O150" s="12"/>
+      <c r="P150" t="s">
+        <v>711</v>
+      </c>
+      <c r="Q150" s="12"/>
+    </row>
+    <row r="151" spans="1:19">
+      <c r="A151" t="s">
+        <v>555</v>
+      </c>
+      <c r="B151" s="12"/>
+      <c r="C151" t="s">
+        <v>559</v>
+      </c>
+      <c r="D151" s="12"/>
+      <c r="N151" t="s">
+        <v>707</v>
+      </c>
+      <c r="O151" s="12"/>
+      <c r="P151" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q151" s="12"/>
+    </row>
+    <row r="152" spans="1:19">
+      <c r="B152" s="12"/>
+      <c r="D152" s="12"/>
+      <c r="O152" s="12"/>
+      <c r="Q152" s="12"/>
+    </row>
+    <row r="153" spans="1:19">
+      <c r="B153" s="12"/>
+      <c r="D153" s="12"/>
+      <c r="O153" s="12"/>
+      <c r="Q153" s="12"/>
+    </row>
+    <row r="154" spans="1:19">
+      <c r="B154" s="12"/>
+      <c r="D154" s="12"/>
+      <c r="O154" s="12"/>
+      <c r="Q154" s="12"/>
+    </row>
+    <row r="157" spans="1:19">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157" t="s">
+        <v>4</v>
+      </c>
+      <c r="D157" t="s">
+        <v>4</v>
+      </c>
+      <c r="F157" t="s">
+        <v>51</v>
+      </c>
+      <c r="N157" t="s">
+        <v>12</v>
+      </c>
+      <c r="O157" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>4</v>
+      </c>
+      <c r="S157" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19">
+      <c r="A158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" s="12">
+        <v>3</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1</v>
+      </c>
+      <c r="D158" s="12">
+        <v>4</v>
+      </c>
+      <c r="E158" t="s">
+        <v>2</v>
+      </c>
+      <c r="F158" t="s">
+        <v>578</v>
+      </c>
+      <c r="N158" t="s">
+        <v>0</v>
+      </c>
+      <c r="O158" s="12">
+        <v>4</v>
+      </c>
+      <c r="P158" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q158" s="12">
+        <v>5</v>
+      </c>
+      <c r="R158" t="s">
+        <v>2</v>
+      </c>
+      <c r="S158" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19">
+      <c r="A159" t="s">
+        <v>570</v>
+      </c>
+      <c r="B159" s="12"/>
+      <c r="C159" t="s">
+        <v>574</v>
+      </c>
+      <c r="D159" s="12"/>
+      <c r="E159">
+        <v>1210</v>
+      </c>
+      <c r="N159" t="s">
+        <v>20</v>
+      </c>
+      <c r="O159" s="12"/>
+      <c r="P159" t="s">
+        <v>710</v>
+      </c>
+      <c r="Q159" s="12"/>
+      <c r="R159">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19">
+      <c r="A160" t="s">
+        <v>571</v>
+      </c>
+      <c r="B160" s="12"/>
+      <c r="C160" t="s">
+        <v>575</v>
+      </c>
+      <c r="D160" s="12"/>
+      <c r="E160">
+        <v>1210</v>
+      </c>
+      <c r="F160" t="s">
+        <v>579</v>
+      </c>
+      <c r="N160" t="s">
+        <v>713</v>
+      </c>
+      <c r="O160" s="12"/>
+      <c r="P160" t="s">
+        <v>716</v>
+      </c>
+      <c r="Q160" s="12"/>
+      <c r="R160">
+        <v>1210</v>
+      </c>
+      <c r="S160" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19">
+      <c r="A161" t="s">
+        <v>572</v>
+      </c>
+      <c r="B161" s="12"/>
+      <c r="C161" t="s">
+        <v>576</v>
+      </c>
+      <c r="D161" s="12"/>
+      <c r="N161" t="s">
+        <v>714</v>
+      </c>
+      <c r="O161" s="12"/>
+      <c r="P161" t="s">
+        <v>718</v>
+      </c>
+      <c r="Q161" s="12"/>
+    </row>
+    <row r="162" spans="1:19">
+      <c r="A162" t="s">
+        <v>573</v>
+      </c>
+      <c r="B162" s="12"/>
+      <c r="C162" t="s">
+        <v>577</v>
+      </c>
+      <c r="D162" s="12"/>
+      <c r="N162" t="s">
+        <v>715</v>
+      </c>
+      <c r="O162" s="12"/>
+      <c r="P162" t="s">
+        <v>723</v>
+      </c>
+      <c r="Q162" s="12"/>
+    </row>
+    <row r="163" spans="1:19">
+      <c r="B163" s="12"/>
+      <c r="D163" s="12"/>
+      <c r="O163" s="12"/>
+      <c r="Q163" s="12"/>
+    </row>
+    <row r="164" spans="1:19">
+      <c r="B164" s="12"/>
+      <c r="D164" s="12"/>
+      <c r="O164" s="12"/>
+      <c r="Q164" s="12"/>
+    </row>
+    <row r="165" spans="1:19">
+      <c r="B165" s="12"/>
+      <c r="D165" s="12"/>
+      <c r="O165" s="12"/>
+      <c r="Q165" s="12"/>
+    </row>
+    <row r="168" spans="1:19">
+      <c r="A168" t="s">
+        <v>581</v>
+      </c>
+      <c r="B168" t="s">
+        <v>4</v>
+      </c>
+      <c r="D168" t="s">
+        <v>4</v>
+      </c>
+      <c r="F168" t="s">
+        <v>51</v>
+      </c>
+      <c r="N168" t="s">
+        <v>581</v>
+      </c>
+      <c r="O168" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>4</v>
+      </c>
+      <c r="S168" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19">
+      <c r="A169" t="s">
+        <v>0</v>
+      </c>
+      <c r="B169" s="12">
+        <v>3</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1</v>
+      </c>
+      <c r="D169" s="12">
+        <v>4</v>
+      </c>
+      <c r="E169" t="s">
+        <v>2</v>
+      </c>
+      <c r="F169" t="s">
+        <v>589</v>
+      </c>
+      <c r="N169" t="s">
+        <v>0</v>
+      </c>
+      <c r="O169" s="12">
+        <v>4</v>
+      </c>
+      <c r="P169" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q169" s="12">
+        <v>5</v>
+      </c>
+      <c r="R169" t="s">
+        <v>2</v>
+      </c>
+      <c r="S169" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19">
+      <c r="A170" t="s">
+        <v>580</v>
+      </c>
+      <c r="B170" s="12"/>
+      <c r="C170" t="s">
+        <v>585</v>
+      </c>
+      <c r="D170" s="12"/>
+      <c r="E170">
+        <v>603</v>
+      </c>
+      <c r="N170" t="s">
+        <v>21</v>
+      </c>
+      <c r="O170" s="12"/>
+      <c r="P170" t="s">
+        <v>688</v>
+      </c>
+      <c r="Q170" s="12"/>
+      <c r="R170">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19">
+      <c r="A171" t="s">
+        <v>582</v>
+      </c>
+      <c r="B171" s="12"/>
+      <c r="C171" t="s">
+        <v>586</v>
+      </c>
+      <c r="D171" s="12"/>
+      <c r="E171">
+        <v>603</v>
+      </c>
+      <c r="F171" t="s">
+        <v>561</v>
+      </c>
+      <c r="N171" t="s">
+        <v>720</v>
+      </c>
+      <c r="O171" s="12"/>
+      <c r="P171" t="s">
+        <v>717</v>
+      </c>
+      <c r="Q171" s="12"/>
+      <c r="R171">
+        <v>603</v>
+      </c>
+      <c r="S171" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19">
+      <c r="A172" t="s">
+        <v>583</v>
+      </c>
+      <c r="B172" s="12"/>
+      <c r="C172" t="s">
+        <v>587</v>
+      </c>
+      <c r="D172" s="12"/>
+      <c r="N172" t="s">
+        <v>721</v>
+      </c>
+      <c r="O172" s="12"/>
+      <c r="P172" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q172" s="12"/>
+    </row>
+    <row r="173" spans="1:19">
+      <c r="A173" t="s">
+        <v>584</v>
+      </c>
+      <c r="B173" s="12"/>
+      <c r="C173" t="s">
+        <v>588</v>
+      </c>
+      <c r="D173" s="12"/>
+      <c r="N173" t="s">
+        <v>722</v>
+      </c>
+      <c r="O173" s="12"/>
+      <c r="P173" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q173" s="12"/>
+    </row>
+    <row r="174" spans="1:19">
+      <c r="B174" s="12"/>
+      <c r="D174" s="12"/>
+      <c r="O174" s="12"/>
+      <c r="Q174" s="12"/>
+    </row>
+    <row r="175" spans="1:19">
+      <c r="B175" s="12"/>
+      <c r="D175" s="12"/>
+      <c r="O175" s="12"/>
+      <c r="Q175" s="12"/>
+    </row>
+    <row r="176" spans="1:19">
+      <c r="B176" s="12"/>
+      <c r="D176" s="12"/>
+      <c r="O176" s="12"/>
+      <c r="Q176" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="K26:K33"/>
+  <mergeCells count="72">
+    <mergeCell ref="O169:O176"/>
+    <mergeCell ref="Q169:Q176"/>
+    <mergeCell ref="O141:O142"/>
+    <mergeCell ref="Q141:Q142"/>
+    <mergeCell ref="O147:O154"/>
+    <mergeCell ref="Q147:Q154"/>
+    <mergeCell ref="O158:O165"/>
+    <mergeCell ref="Q158:Q165"/>
+    <mergeCell ref="O121:O122"/>
+    <mergeCell ref="Q121:Q122"/>
+    <mergeCell ref="O125:O126"/>
+    <mergeCell ref="Q125:Q126"/>
+    <mergeCell ref="O131:O138"/>
+    <mergeCell ref="Q131:Q138"/>
+    <mergeCell ref="O95:O102"/>
+    <mergeCell ref="Q95:Q102"/>
+    <mergeCell ref="O105:O112"/>
+    <mergeCell ref="Q105:Q112"/>
+    <mergeCell ref="O115:O116"/>
+    <mergeCell ref="Q115:Q116"/>
+    <mergeCell ref="O73:O74"/>
+    <mergeCell ref="Q73:Q74"/>
+    <mergeCell ref="O79:O80"/>
+    <mergeCell ref="Q79:Q80"/>
+    <mergeCell ref="O84:O91"/>
+    <mergeCell ref="Q84:Q91"/>
+    <mergeCell ref="O44:O51"/>
+    <mergeCell ref="Q44:Q51"/>
+    <mergeCell ref="O55:O62"/>
+    <mergeCell ref="Q55:Q62"/>
+    <mergeCell ref="O67:O69"/>
+    <mergeCell ref="Q67:Q69"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="B44:B51"/>
+    <mergeCell ref="D44:D51"/>
+    <mergeCell ref="B55:B62"/>
+    <mergeCell ref="D55:D62"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="B29:B36"/>
+    <mergeCell ref="D29:D36"/>
+    <mergeCell ref="K15:K22"/>
     <mergeCell ref="D2:D9"/>
     <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="D26:D33"/>
-    <mergeCell ref="I26:I33"/>
+    <mergeCell ref="B15:B22"/>
+    <mergeCell ref="D15:D22"/>
+    <mergeCell ref="I15:I22"/>
+    <mergeCell ref="B84:B91"/>
+    <mergeCell ref="D84:D91"/>
+    <mergeCell ref="B95:B102"/>
+    <mergeCell ref="D95:D102"/>
+    <mergeCell ref="B105:B112"/>
+    <mergeCell ref="D105:D112"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="D125:D126"/>
+    <mergeCell ref="B158:B165"/>
+    <mergeCell ref="D158:D165"/>
+    <mergeCell ref="B169:B176"/>
+    <mergeCell ref="D169:D176"/>
+    <mergeCell ref="B131:B138"/>
+    <mergeCell ref="D131:D138"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="D141:D142"/>
+    <mergeCell ref="B147:B154"/>
+    <mergeCell ref="D147:D154"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D596A7B6-3493-4889-918C-0138A853E649}">
-  <dimension ref="A1:F111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R167"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="10.6640625" style="2"/>
+    <col min="5" max="5" width="10.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>56</v>
       </c>
@@ -1388,18 +5659,31 @@
       <c r="F1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K1">
+        <v>0</v>
+      </c>
+      <c r="L1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="2"/>
+      <c r="P1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="12">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1408,99 +5692,197 @@
       <c r="F2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12">
+        <v>2</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="12">
+        <v>3</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="12"/>
       <c r="C3" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K3" t="s">
+        <v>292</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" t="s">
+        <v>302</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="12"/>
       <c r="C4" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>293</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" t="s">
+        <v>303</v>
+      </c>
+      <c r="N4" s="12"/>
+      <c r="O4" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="12"/>
       <c r="C5" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="12"/>
       <c r="E5" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>294</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" t="s">
+        <v>304</v>
+      </c>
+      <c r="N5" s="12"/>
+      <c r="O5" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="12"/>
       <c r="C6" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="12"/>
       <c r="E6" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>295</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" t="s">
+        <v>305</v>
+      </c>
+      <c r="N6" s="12"/>
+      <c r="O6" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="12"/>
       <c r="C7" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="12"/>
       <c r="E7" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K7" t="s">
+        <v>296</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" t="s">
+        <v>306</v>
+      </c>
+      <c r="N7" s="12"/>
+      <c r="O7" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="12"/>
       <c r="C8" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="12"/>
       <c r="E8" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K8" t="s">
+        <v>297</v>
+      </c>
+      <c r="L8" s="12"/>
+      <c r="M8" t="s">
+        <v>307</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="12"/>
       <c r="C9" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="12"/>
       <c r="E9" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K9" t="s">
+        <v>298</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" t="s">
+        <v>308</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>64</v>
       </c>
@@ -1510,8 +5892,45 @@
       <c r="E10" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>299</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" t="s">
+        <v>309</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="K11" t="s">
+        <v>300</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" t="s">
+        <v>310</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="K12" t="s">
+        <v>301</v>
+      </c>
+      <c r="L12" s="12"/>
+      <c r="M12" t="s">
+        <v>311</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -1525,17 +5944,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="12">
         <v>1</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="12">
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -1544,54 +5963,153 @@
       <c r="F14" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K14">
+        <v>49.9</v>
+      </c>
+      <c r="L14" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="12"/>
       <c r="C15" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="12"/>
       <c r="E15" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K15" t="s">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12">
+        <v>2</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="12">
+        <v>3</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="12"/>
       <c r="C16" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="12"/>
       <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="3"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>313</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" t="s">
+        <v>331</v>
+      </c>
+      <c r="N16" s="12"/>
+      <c r="O16">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="B17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="K17" t="s">
+        <v>314</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" t="s">
+        <v>332</v>
+      </c>
+      <c r="N17" s="12"/>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="B18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="K18" t="s">
+        <v>315</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" t="s">
+        <v>333</v>
+      </c>
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="B19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="K19" t="s">
+        <v>316</v>
+      </c>
+      <c r="L19" s="12"/>
+      <c r="M19" t="s">
+        <v>334</v>
+      </c>
+      <c r="N19" s="12"/>
+      <c r="O19" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="B20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="K20" t="s">
+        <v>317</v>
+      </c>
+      <c r="L20" s="12"/>
+      <c r="M20" t="s">
+        <v>335</v>
+      </c>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="B21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="K21" t="s">
+        <v>318</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" t="s">
+        <v>336</v>
+      </c>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="K22" t="s">
+        <v>319</v>
+      </c>
+      <c r="L22" s="12"/>
+      <c r="M22" t="s">
+        <v>337</v>
+      </c>
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>0</v>
       </c>
@@ -1604,18 +6122,26 @@
       <c r="F23" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K23" t="s">
+        <v>320</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" t="s">
+        <v>338</v>
+      </c>
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="12">
         <v>1</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="12">
         <v>2</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -1624,63 +6150,147 @@
       <c r="F24" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K24" t="s">
+        <v>321</v>
+      </c>
+      <c r="L24" s="12"/>
+      <c r="M24" t="s">
+        <v>339</v>
+      </c>
+      <c r="N24" s="12"/>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="3"/>
+      <c r="B25" s="12"/>
       <c r="C25" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="12"/>
       <c r="E25" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K25" t="s">
+        <v>322</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" t="s">
+        <v>340</v>
+      </c>
+      <c r="N25" s="12"/>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="3"/>
+      <c r="B26" s="12"/>
       <c r="C26" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="12"/>
       <c r="E26" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K26" t="s">
+        <v>323</v>
+      </c>
+      <c r="L26" s="12"/>
+      <c r="M26" t="s">
+        <v>341</v>
+      </c>
+      <c r="N26" s="12"/>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="3"/>
+      <c r="B27" s="12"/>
       <c r="C27" t="s">
         <v>88</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="12"/>
       <c r="E27" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K27" t="s">
+        <v>324</v>
+      </c>
+      <c r="L27" s="12"/>
+      <c r="M27" t="s">
+        <v>342</v>
+      </c>
+      <c r="N27" s="12"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="B28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="K28" t="s">
+        <v>325</v>
+      </c>
+      <c r="L28" s="12"/>
+      <c r="M28" t="s">
+        <v>343</v>
+      </c>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="B29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="K29" t="s">
+        <v>326</v>
+      </c>
+      <c r="L29" s="12"/>
+      <c r="M29" t="s">
+        <v>344</v>
+      </c>
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="B30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="K30" t="s">
+        <v>327</v>
+      </c>
+      <c r="L30" s="12"/>
+      <c r="M30" t="s">
+        <v>345</v>
+      </c>
+      <c r="N30" s="12"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="B31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="K31" t="s">
+        <v>328</v>
+      </c>
+      <c r="L31" s="12"/>
+      <c r="M31" t="s">
+        <v>346</v>
+      </c>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="K32" t="s">
+        <v>329</v>
+      </c>
+      <c r="L32" s="12"/>
+      <c r="M32" t="s">
+        <v>347</v>
+      </c>
+      <c r="N32" s="12"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="K33" t="s">
+        <v>330</v>
+      </c>
+      <c r="L33" s="12"/>
+      <c r="M33" t="s">
+        <v>348</v>
+      </c>
+      <c r="N33" s="12"/>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>84</v>
       </c>
@@ -1694,17 +6304,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="12">
         <v>1</v>
       </c>
       <c r="C35" t="s">
         <v>1</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="12">
         <v>2</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -1714,44 +6324,136 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="3"/>
+      <c r="B36" s="12"/>
       <c r="C36" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="12"/>
       <c r="E36" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="3"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="3"/>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="3"/>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="3"/>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="3"/>
-      <c r="D42" s="3"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K36" t="s">
+        <v>350</v>
+      </c>
+      <c r="L36" t="s">
+        <v>4</v>
+      </c>
+      <c r="N36" t="s">
+        <v>4</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="B37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="K37" t="s">
+        <v>0</v>
+      </c>
+      <c r="L37" s="12">
+        <v>2</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1</v>
+      </c>
+      <c r="N37" s="12">
+        <v>3</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P37" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="B38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="K38" t="s">
+        <v>353</v>
+      </c>
+      <c r="L38" s="12"/>
+      <c r="M38" t="s">
+        <v>351</v>
+      </c>
+      <c r="N38" s="12"/>
+      <c r="O38" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="B39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="K39" t="s">
+        <v>354</v>
+      </c>
+      <c r="L39" s="12"/>
+      <c r="M39" t="s">
+        <v>352</v>
+      </c>
+      <c r="N39" s="12"/>
+      <c r="O39" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="B40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="L40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="2"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="B41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="L41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="B42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42" t="s">
+        <v>4</v>
+      </c>
+      <c r="N42" t="s">
+        <v>4</v>
+      </c>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="K43" t="s">
+        <v>0</v>
+      </c>
+      <c r="L43" s="12">
+        <v>2</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1</v>
+      </c>
+      <c r="N43" s="12">
+        <v>3</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P43" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>93</v>
       </c>
@@ -1764,18 +6466,29 @@
       <c r="F44" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K44" t="s">
+        <v>358</v>
+      </c>
+      <c r="L44" s="12"/>
+      <c r="M44" t="s">
+        <v>365</v>
+      </c>
+      <c r="N44" s="12"/>
+      <c r="O44" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>0</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="12">
         <v>1</v>
       </c>
       <c r="C45" t="s">
         <v>1</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="12">
         <v>2</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -1784,54 +6497,118 @@
       <c r="F45" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K45" t="s">
+        <v>359</v>
+      </c>
+      <c r="L45" s="12"/>
+      <c r="M45" t="s">
+        <v>364</v>
+      </c>
+      <c r="N45" s="12"/>
+      <c r="O45" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>94</v>
       </c>
-      <c r="B46" s="3"/>
+      <c r="B46" s="12"/>
       <c r="C46" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="3"/>
+      <c r="D46" s="12"/>
       <c r="E46" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="3"/>
+      <c r="B47" s="12"/>
       <c r="C47" t="s">
         <v>97</v>
       </c>
-      <c r="D47" s="3"/>
+      <c r="D47" s="12"/>
       <c r="E47" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="3"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B50" s="3"/>
-      <c r="D50" s="3"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="3"/>
-      <c r="D52" s="3"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16">
+      <c r="B48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="K48" t="s">
+        <v>357</v>
+      </c>
+      <c r="L48" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="B49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="K49" t="s">
+        <v>0</v>
+      </c>
+      <c r="L49" s="12">
+        <v>2</v>
+      </c>
+      <c r="M49" t="s">
+        <v>1</v>
+      </c>
+      <c r="N49" s="12">
+        <v>3</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P49" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="B50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="K50" t="s">
+        <v>360</v>
+      </c>
+      <c r="L50" s="12"/>
+      <c r="M50" t="s">
+        <v>363</v>
+      </c>
+      <c r="N50" s="12"/>
+      <c r="O50" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="B51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="K51" t="s">
+        <v>361</v>
+      </c>
+      <c r="L51" s="12"/>
+      <c r="M51" t="s">
+        <v>362</v>
+      </c>
+      <c r="N51" s="12"/>
+      <c r="O51" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="B52" s="12"/>
+      <c r="D52" s="12"/>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55">
         <v>332</v>
       </c>
@@ -1845,17 +6622,17 @@
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18">
       <c r="A56" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="12">
         <v>1</v>
       </c>
       <c r="C56" t="s">
         <v>1</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="12">
         <v>2</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -1865,44 +6642,108 @@
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18">
       <c r="A57" t="s">
         <v>100</v>
       </c>
-      <c r="B57" s="3"/>
+      <c r="B57" s="12"/>
       <c r="C57" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="12"/>
       <c r="E57" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="3"/>
-      <c r="D58" s="3"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="3"/>
-      <c r="D59" s="3"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B60" s="3"/>
-      <c r="D60" s="3"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="3"/>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="3"/>
-      <c r="D62" s="3"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="3"/>
-      <c r="D63" s="3"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18">
+      <c r="B58" s="12"/>
+      <c r="D58" s="12"/>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="B59" s="12"/>
+      <c r="D59" s="12"/>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="B60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="K60">
+        <v>100</v>
+      </c>
+      <c r="L60" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="B61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="K61" t="s">
+        <v>0</v>
+      </c>
+      <c r="L61" s="12">
+        <v>3</v>
+      </c>
+      <c r="M61" t="s">
+        <v>1</v>
+      </c>
+      <c r="N61" s="12">
+        <v>4</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P61" t="s">
+        <v>366</v>
+      </c>
+      <c r="R61" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="B62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="K62" t="s">
+        <v>667</v>
+      </c>
+      <c r="L62" s="12"/>
+      <c r="M62" t="s">
+        <v>671</v>
+      </c>
+      <c r="N62" s="12"/>
+      <c r="O62" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="B63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="K63" t="s">
+        <v>668</v>
+      </c>
+      <c r="L63" s="12"/>
+      <c r="M63" t="s">
+        <v>672</v>
+      </c>
+      <c r="N63" s="12"/>
+      <c r="O63" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="K64" t="s">
+        <v>669</v>
+      </c>
+      <c r="M64" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
       <c r="A65" t="s">
         <v>102</v>
       </c>
@@ -1915,18 +6756,24 @@
       <c r="F65" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K65" t="s">
+        <v>670</v>
+      </c>
+      <c r="M65" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66" t="s">
         <v>0</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="12">
         <v>1</v>
       </c>
       <c r="C66" t="s">
         <v>1</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="12">
         <v>2</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -1936,89 +6783,196 @@
         <v>115</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18">
       <c r="A67" t="s">
         <v>103</v>
       </c>
-      <c r="B67" s="3"/>
+      <c r="B67" s="12"/>
       <c r="C67" t="s">
         <v>109</v>
       </c>
-      <c r="D67" s="3"/>
+      <c r="D67" s="12"/>
       <c r="E67" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18">
       <c r="A68" t="s">
         <v>104</v>
       </c>
-      <c r="B68" s="3"/>
+      <c r="B68" s="12"/>
       <c r="C68" t="s">
         <v>110</v>
       </c>
-      <c r="D68" s="3"/>
+      <c r="D68" s="12"/>
       <c r="E68" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K68">
+        <v>10</v>
+      </c>
+      <c r="L68" t="s">
+        <v>4</v>
+      </c>
+      <c r="N68" t="s">
+        <v>4</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
       <c r="A69" t="s">
         <v>105</v>
       </c>
-      <c r="B69" s="3"/>
+      <c r="B69" s="12"/>
       <c r="C69" t="s">
         <v>111</v>
       </c>
-      <c r="D69" s="3"/>
+      <c r="D69" s="12"/>
       <c r="E69" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K69" t="s">
+        <v>0</v>
+      </c>
+      <c r="L69" s="12">
+        <v>3</v>
+      </c>
+      <c r="M69" t="s">
+        <v>1</v>
+      </c>
+      <c r="N69" s="12">
+        <v>4</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P69" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
       <c r="A70" t="s">
         <v>106</v>
       </c>
-      <c r="B70" s="3"/>
+      <c r="B70" s="12"/>
       <c r="C70" t="s">
         <v>112</v>
       </c>
-      <c r="D70" s="3"/>
+      <c r="D70" s="12"/>
       <c r="E70" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K70" t="s">
+        <v>411</v>
+      </c>
+      <c r="L70" s="12"/>
+      <c r="M70" t="s">
+        <v>412</v>
+      </c>
+      <c r="N70" s="12"/>
+      <c r="O70" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="3"/>
+      <c r="B71" s="12"/>
       <c r="C71" t="s">
         <v>113</v>
       </c>
-      <c r="D71" s="3"/>
+      <c r="D71" s="12"/>
       <c r="E71" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="L71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="2"/>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72" t="s">
         <v>108</v>
       </c>
-      <c r="B72" s="3"/>
+      <c r="B72" s="12"/>
       <c r="C72" t="s">
         <v>114</v>
       </c>
-      <c r="D72" s="3"/>
+      <c r="D72" s="12"/>
       <c r="E72" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B73" s="3"/>
-      <c r="D73" s="3"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18">
+      <c r="B73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="K73" t="s">
+        <v>430</v>
+      </c>
+      <c r="L73" t="s">
+        <v>4</v>
+      </c>
+      <c r="N73" t="s">
+        <v>4</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="K74" t="s">
+        <v>0</v>
+      </c>
+      <c r="L74" s="12">
+        <v>3</v>
+      </c>
+      <c r="M74" t="s">
+        <v>1</v>
+      </c>
+      <c r="N74" s="12">
+        <v>4</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P74" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="K75" t="s">
+        <v>431</v>
+      </c>
+      <c r="L75" s="12"/>
+      <c r="M75" t="s">
+        <v>433</v>
+      </c>
+      <c r="N75" s="12"/>
+      <c r="O75" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="K76" t="s">
+        <v>432</v>
+      </c>
+      <c r="L76" s="12"/>
+      <c r="M76" t="s">
+        <v>434</v>
+      </c>
+      <c r="N76" s="12"/>
+      <c r="O76" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R76" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77">
         <v>100</v>
       </c>
@@ -2031,18 +6985,27 @@
       <c r="F77" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K77" t="s">
+        <v>435</v>
+      </c>
+      <c r="M77" t="s">
+        <v>437</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78" t="s">
         <v>0</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="12">
         <v>1</v>
       </c>
       <c r="C78" t="s">
         <v>1</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="12">
         <v>2</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -2051,90 +7014,161 @@
       <c r="F78" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K78" t="s">
+        <v>436</v>
+      </c>
+      <c r="M78" t="s">
+        <v>438</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79" t="s">
         <v>122</v>
       </c>
-      <c r="B79" s="3"/>
+      <c r="B79" s="12"/>
       <c r="C79" t="s">
         <v>116</v>
       </c>
-      <c r="D79" s="3"/>
+      <c r="D79" s="12"/>
       <c r="E79" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K79" t="s">
+        <v>440</v>
+      </c>
+      <c r="M79" t="s">
+        <v>441</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80" t="s">
         <v>123</v>
       </c>
-      <c r="B80" s="3"/>
+      <c r="B80" s="12"/>
       <c r="C80" t="s">
         <v>117</v>
       </c>
-      <c r="D80" s="3"/>
+      <c r="D80" s="12"/>
       <c r="E80" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16">
       <c r="A81" t="s">
         <v>124</v>
       </c>
-      <c r="B81" s="3"/>
+      <c r="B81" s="12"/>
       <c r="C81" t="s">
         <v>118</v>
       </c>
-      <c r="D81" s="3"/>
+      <c r="D81" s="12"/>
       <c r="E81" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16">
       <c r="A82" t="s">
         <v>125</v>
       </c>
-      <c r="B82" s="3"/>
+      <c r="B82" s="12"/>
       <c r="C82" t="s">
         <v>119</v>
       </c>
-      <c r="D82" s="3"/>
+      <c r="D82" s="12"/>
       <c r="E82" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K82" t="s">
+        <v>442</v>
+      </c>
+      <c r="L82" t="s">
+        <v>4</v>
+      </c>
+      <c r="N82" t="s">
+        <v>4</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83" t="s">
         <v>126</v>
       </c>
-      <c r="B83" s="3"/>
+      <c r="B83" s="12"/>
       <c r="C83" t="s">
         <v>120</v>
       </c>
-      <c r="D83" s="3"/>
+      <c r="D83" s="12"/>
       <c r="E83" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K83" t="s">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1">
+        <v>3</v>
+      </c>
+      <c r="M83" t="s">
+        <v>1</v>
+      </c>
+      <c r="N83" s="1">
+        <v>4</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P83" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84" t="s">
         <v>127</v>
       </c>
-      <c r="B84" s="3"/>
+      <c r="B84" s="12"/>
       <c r="C84" t="s">
         <v>121</v>
       </c>
-      <c r="D84" s="3"/>
+      <c r="D84" s="12"/>
       <c r="E84" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B85" s="3"/>
-      <c r="D85" s="3"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K84" t="s">
+        <v>443</v>
+      </c>
+      <c r="L84" s="1"/>
+      <c r="M84" t="s">
+        <v>445</v>
+      </c>
+      <c r="N84" s="1"/>
+      <c r="O84" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="B85" s="12"/>
+      <c r="D85" s="12"/>
+      <c r="K85" t="s">
+        <v>444</v>
+      </c>
+      <c r="L85" s="1"/>
+      <c r="M85" t="s">
+        <v>446</v>
+      </c>
+      <c r="N85" s="1"/>
+      <c r="O85" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88" t="s">
         <v>129</v>
       </c>
@@ -2147,139 +7181,237 @@
       <c r="F88" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K88">
+        <v>499</v>
+      </c>
+      <c r="L88" t="s">
+        <v>4</v>
+      </c>
+      <c r="N88" t="s">
+        <v>4</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89" t="s">
         <v>0</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="12">
         <v>1</v>
       </c>
       <c r="C89" t="s">
         <v>1</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="12">
         <v>2</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K89" t="s">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1">
+        <v>3</v>
+      </c>
+      <c r="M89" t="s">
+        <v>1</v>
+      </c>
+      <c r="N89" s="1">
+        <v>4</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P89" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
       <c r="A90" t="s">
         <v>130</v>
       </c>
-      <c r="B90" s="3"/>
+      <c r="B90" s="12"/>
       <c r="C90" t="s">
         <v>137</v>
       </c>
-      <c r="D90" s="3"/>
+      <c r="D90" s="12"/>
       <c r="E90" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F90" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K90" t="s">
+        <v>453</v>
+      </c>
+      <c r="L90" s="1"/>
+      <c r="M90" t="s">
+        <v>457</v>
+      </c>
+      <c r="N90" s="1"/>
+      <c r="O90" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
       <c r="A91" t="s">
         <v>131</v>
       </c>
-      <c r="B91" s="3"/>
+      <c r="B91" s="12"/>
       <c r="C91" t="s">
         <v>138</v>
       </c>
-      <c r="D91" s="3"/>
+      <c r="D91" s="12"/>
       <c r="E91" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="F91" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K91" t="s">
+        <v>454</v>
+      </c>
+      <c r="L91" s="1"/>
+      <c r="M91" t="s">
+        <v>458</v>
+      </c>
+      <c r="N91" s="1"/>
+      <c r="O91" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92" t="s">
         <v>132</v>
       </c>
-      <c r="B92" s="3"/>
+      <c r="B92" s="12"/>
       <c r="C92" t="s">
         <v>139</v>
       </c>
-      <c r="D92" s="3"/>
+      <c r="D92" s="12"/>
       <c r="E92" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="F92" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K92" t="s">
+        <v>455</v>
+      </c>
+      <c r="M92" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93" t="s">
         <v>133</v>
       </c>
-      <c r="B93" s="3"/>
+      <c r="B93" s="12"/>
       <c r="C93" t="s">
         <v>140</v>
       </c>
-      <c r="D93" s="3"/>
+      <c r="D93" s="12"/>
       <c r="E93" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="F93" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K93" t="s">
+        <v>456</v>
+      </c>
+      <c r="M93" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
       <c r="A94" t="s">
         <v>134</v>
       </c>
-      <c r="B94" s="3"/>
+      <c r="B94" s="12"/>
       <c r="C94" t="s">
         <v>141</v>
       </c>
-      <c r="D94" s="3"/>
+      <c r="D94" s="12"/>
       <c r="E94" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="F94" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16">
       <c r="A95" t="s">
         <v>135</v>
       </c>
-      <c r="B95" s="3"/>
+      <c r="B95" s="12"/>
       <c r="C95" t="s">
         <v>142</v>
       </c>
-      <c r="D95" s="3"/>
+      <c r="D95" s="12"/>
       <c r="E95" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="F95" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16">
       <c r="A96" t="s">
         <v>136</v>
       </c>
-      <c r="B96" s="3"/>
+      <c r="B96" s="12"/>
       <c r="C96" t="s">
         <v>143</v>
       </c>
-      <c r="D96" s="3"/>
+      <c r="D96" s="12"/>
       <c r="E96" s="2" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="F96" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K96" t="s">
+        <v>526</v>
+      </c>
+      <c r="L96" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="K97" t="s">
+        <v>0</v>
+      </c>
+      <c r="L97" s="1">
+        <v>3</v>
+      </c>
+      <c r="M97" t="s">
+        <v>1</v>
+      </c>
+      <c r="N97" s="1">
+        <v>4</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P97" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
@@ -2290,18 +7422,32 @@
       <c r="F98" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="K98" t="s">
+        <v>525</v>
+      </c>
+      <c r="L98" s="1"/>
+      <c r="M98" t="s">
+        <v>527</v>
+      </c>
+      <c r="N98" s="1"/>
+      <c r="O98" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P98" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99" s="12">
         <v>1</v>
       </c>
       <c r="C99" t="s">
         <v>1</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="12">
         <v>2</v>
       </c>
       <c r="E99" s="2" t="s">
@@ -2310,122 +7456,788 @@
       <c r="F99" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="L99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="O99" s="2"/>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100" t="s">
-        <v>148</v>
-      </c>
-      <c r="B100" s="3"/>
+        <v>147</v>
+      </c>
+      <c r="B100" s="12"/>
       <c r="C100" t="s">
-        <v>160</v>
-      </c>
-      <c r="D100" s="3"/>
+        <v>159</v>
+      </c>
+      <c r="D100" s="12"/>
       <c r="E100" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16">
       <c r="A101" t="s">
+        <v>148</v>
+      </c>
+      <c r="B101" s="12"/>
+      <c r="C101" t="s">
+        <v>160</v>
+      </c>
+      <c r="D101" s="12"/>
+      <c r="K101" t="s">
+        <v>529</v>
+      </c>
+      <c r="L101" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" t="s">
+        <v>4</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" t="s">
         <v>149</v>
       </c>
-      <c r="B101" s="3"/>
-      <c r="C101" t="s">
+      <c r="B102" s="12"/>
+      <c r="C102" t="s">
         <v>161</v>
       </c>
-      <c r="D101" s="3"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+      <c r="D102" s="12"/>
+      <c r="K102" t="s">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1">
+        <v>3</v>
+      </c>
+      <c r="M102" t="s">
+        <v>1</v>
+      </c>
+      <c r="N102" s="1">
+        <v>4</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P102" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" t="s">
         <v>150</v>
       </c>
-      <c r="B102" s="3"/>
-      <c r="C102" t="s">
+      <c r="B103" s="12"/>
+      <c r="C103" t="s">
         <v>162</v>
       </c>
-      <c r="D102" s="3"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+      <c r="D103" s="12"/>
+      <c r="K103" t="s">
+        <v>530</v>
+      </c>
+      <c r="L103" s="1"/>
+      <c r="M103" t="s">
+        <v>531</v>
+      </c>
+      <c r="N103" s="1"/>
+      <c r="O103" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P103" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104" t="s">
         <v>151</v>
       </c>
-      <c r="B103" s="3"/>
-      <c r="C103" t="s">
+      <c r="B104" s="12"/>
+      <c r="C104" t="s">
         <v>163</v>
       </c>
-      <c r="D103" s="3"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+      <c r="D104" s="12"/>
+      <c r="L104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="2"/>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105" t="s">
         <v>152</v>
       </c>
-      <c r="B104" s="3"/>
-      <c r="C104" t="s">
+      <c r="B105" s="12"/>
+      <c r="C105" t="s">
         <v>164</v>
       </c>
-      <c r="D104" s="3"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+      <c r="D105" s="12"/>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106" t="s">
         <v>153</v>
       </c>
-      <c r="B105" s="3"/>
-      <c r="C105" t="s">
+      <c r="B106" s="12"/>
+      <c r="C106" t="s">
         <v>165</v>
       </c>
-      <c r="D105" s="3"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+      <c r="D106" s="12"/>
+    </row>
+    <row r="107" spans="1:16">
+      <c r="A107" t="s">
         <v>154</v>
       </c>
-      <c r="B106" s="3"/>
-      <c r="C106" t="s">
+      <c r="C107" t="s">
         <v>166</v>
       </c>
-      <c r="D106" s="3"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+      <c r="K107">
+        <v>3.3</v>
+      </c>
+      <c r="L107" t="s">
+        <v>4</v>
+      </c>
+      <c r="N107" t="s">
+        <v>4</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
+      <c r="A108" t="s">
         <v>155</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C108" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
+      <c r="K108" t="s">
+        <v>0</v>
+      </c>
+      <c r="L108" s="1">
+        <v>3</v>
+      </c>
+      <c r="M108" t="s">
+        <v>1</v>
+      </c>
+      <c r="N108" s="1">
+        <v>4</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P108" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109" t="s">
         <v>156</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C109" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
+      <c r="K109" t="s">
+        <v>590</v>
+      </c>
+      <c r="L109" s="1"/>
+      <c r="M109" t="s">
+        <v>597</v>
+      </c>
+      <c r="N109" s="1"/>
+      <c r="O109" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110" t="s">
         <v>157</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C110" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
+      <c r="K110" t="s">
+        <v>591</v>
+      </c>
+      <c r="L110" s="1"/>
+      <c r="M110" t="s">
+        <v>596</v>
+      </c>
+      <c r="N110" s="1"/>
+      <c r="O110" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P110">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111" t="s">
         <v>158</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C111" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>159</v>
-      </c>
-      <c r="C111" t="s">
-        <v>171</v>
+      <c r="K111" t="s">
+        <v>592</v>
+      </c>
+      <c r="M111" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="K112" t="s">
+        <v>593</v>
+      </c>
+      <c r="M112" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="115" spans="11:18">
+      <c r="K115">
+        <v>10</v>
+      </c>
+      <c r="L115" t="s">
+        <v>4</v>
+      </c>
+      <c r="N115" t="s">
+        <v>4</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="116" spans="11:18">
+      <c r="K116" t="s">
+        <v>0</v>
+      </c>
+      <c r="L116" s="1">
+        <v>4</v>
+      </c>
+      <c r="M116" t="s">
+        <v>1</v>
+      </c>
+      <c r="N116" s="1">
+        <v>5</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P116" t="s">
+        <v>413</v>
+      </c>
+      <c r="R116" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="117" spans="11:18">
+      <c r="K117" t="s">
+        <v>632</v>
+      </c>
+      <c r="L117" s="1"/>
+      <c r="M117" t="s">
+        <v>633</v>
+      </c>
+      <c r="N117" s="1"/>
+      <c r="O117" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="118" spans="11:18">
+      <c r="L118" s="1"/>
+      <c r="N118" s="1"/>
+      <c r="O118" s="2"/>
+    </row>
+    <row r="120" spans="11:18">
+      <c r="K120" t="s">
+        <v>430</v>
+      </c>
+      <c r="L120" t="s">
+        <v>4</v>
+      </c>
+      <c r="N120" t="s">
+        <v>4</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="121" spans="11:18">
+      <c r="K121" t="s">
+        <v>0</v>
+      </c>
+      <c r="L121" s="1">
+        <v>4</v>
+      </c>
+      <c r="M121" t="s">
+        <v>1</v>
+      </c>
+      <c r="N121" s="1">
+        <v>5</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P121" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="122" spans="11:18">
+      <c r="K122" t="s">
+        <v>138</v>
+      </c>
+      <c r="L122" s="1"/>
+      <c r="M122" t="s">
+        <v>635</v>
+      </c>
+      <c r="N122" s="1"/>
+      <c r="O122" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" spans="11:18">
+      <c r="K123" t="s">
+        <v>139</v>
+      </c>
+      <c r="L123" s="1"/>
+      <c r="M123" t="s">
+        <v>636</v>
+      </c>
+      <c r="N123" s="1"/>
+      <c r="O123" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R123" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="124" spans="11:18">
+      <c r="K124" t="s">
+        <v>141</v>
+      </c>
+      <c r="M124" t="s">
+        <v>637</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" spans="11:18">
+      <c r="K125" t="s">
+        <v>142</v>
+      </c>
+      <c r="M125" t="s">
+        <v>638</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" spans="11:18">
+      <c r="K126" t="s">
+        <v>140</v>
+      </c>
+      <c r="M126" t="s">
+        <v>639</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" spans="11:18">
+      <c r="K129" t="s">
+        <v>442</v>
+      </c>
+      <c r="L129" t="s">
+        <v>4</v>
+      </c>
+      <c r="N129" t="s">
+        <v>4</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="130" spans="11:18">
+      <c r="K130" t="s">
+        <v>0</v>
+      </c>
+      <c r="L130" s="1">
+        <v>4</v>
+      </c>
+      <c r="M130" t="s">
+        <v>1</v>
+      </c>
+      <c r="N130" s="1">
+        <v>5</v>
+      </c>
+      <c r="O130" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P130" t="s">
+        <v>447</v>
+      </c>
+      <c r="R130" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="131" spans="11:18">
+      <c r="K131" t="s">
+        <v>121</v>
+      </c>
+      <c r="L131" s="1"/>
+      <c r="M131" t="s">
+        <v>640</v>
+      </c>
+      <c r="N131" s="1"/>
+      <c r="O131" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" spans="11:18">
+      <c r="K132" t="s">
+        <v>120</v>
+      </c>
+      <c r="L132" s="1"/>
+      <c r="M132" t="s">
+        <v>641</v>
+      </c>
+      <c r="N132" s="1"/>
+      <c r="O132" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="135" spans="11:18">
+      <c r="K135">
+        <v>499</v>
+      </c>
+      <c r="L135" t="s">
+        <v>4</v>
+      </c>
+      <c r="N135" t="s">
+        <v>4</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="136" spans="11:18">
+      <c r="K136" t="s">
+        <v>0</v>
+      </c>
+      <c r="L136" s="1">
+        <v>4</v>
+      </c>
+      <c r="M136" t="s">
+        <v>1</v>
+      </c>
+      <c r="N136" s="1">
+        <v>5</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P136" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="137" spans="11:18">
+      <c r="K137" t="s">
+        <v>65</v>
+      </c>
+      <c r="L137" s="1"/>
+      <c r="M137" t="s">
+        <v>642</v>
+      </c>
+      <c r="N137" s="1"/>
+      <c r="O137" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="138" spans="11:18">
+      <c r="K138" t="s">
+        <v>67</v>
+      </c>
+      <c r="L138" s="1"/>
+      <c r="M138" t="s">
+        <v>643</v>
+      </c>
+      <c r="N138" s="1"/>
+      <c r="O138" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="139" spans="11:18">
+      <c r="K139" t="s">
+        <v>69</v>
+      </c>
+      <c r="M139" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="140" spans="11:18">
+      <c r="K140" t="s">
+        <v>71</v>
+      </c>
+      <c r="M140" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="143" spans="11:18">
+      <c r="K143" t="s">
+        <v>526</v>
+      </c>
+      <c r="L143" t="s">
+        <v>4</v>
+      </c>
+      <c r="N143" t="s">
+        <v>4</v>
+      </c>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="144" spans="11:18">
+      <c r="K144" t="s">
+        <v>0</v>
+      </c>
+      <c r="L144" s="1">
+        <v>4</v>
+      </c>
+      <c r="M144" t="s">
+        <v>1</v>
+      </c>
+      <c r="N144" s="1">
+        <v>5</v>
+      </c>
+      <c r="O144" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P144" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="145" spans="11:16">
+      <c r="K145" t="s">
+        <v>118</v>
+      </c>
+      <c r="L145" s="1"/>
+      <c r="M145" t="s">
+        <v>725</v>
+      </c>
+      <c r="N145" s="1"/>
+      <c r="O145" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="146" spans="11:16">
+      <c r="L146" s="1"/>
+      <c r="N146" s="1"/>
+      <c r="O146" s="2"/>
+    </row>
+    <row r="148" spans="11:16">
+      <c r="O148" s="2"/>
+    </row>
+    <row r="149" spans="11:16">
+      <c r="L149" s="1"/>
+      <c r="N149" s="1"/>
+      <c r="O149" s="2"/>
+    </row>
+    <row r="150" spans="11:16">
+      <c r="L150" s="1"/>
+      <c r="N150" s="1"/>
+      <c r="O150" s="2"/>
+    </row>
+    <row r="151" spans="11:16">
+      <c r="L151" s="1"/>
+      <c r="N151" s="1"/>
+      <c r="O151" s="2"/>
+    </row>
+    <row r="154" spans="11:16">
+      <c r="K154">
+        <v>3.3</v>
+      </c>
+      <c r="L154" t="s">
+        <v>4</v>
+      </c>
+      <c r="N154" t="s">
+        <v>4</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="155" spans="11:16">
+      <c r="K155" t="s">
+        <v>0</v>
+      </c>
+      <c r="L155" s="1">
+        <v>4</v>
+      </c>
+      <c r="M155" t="s">
+        <v>1</v>
+      </c>
+      <c r="N155" s="1">
+        <v>5</v>
+      </c>
+      <c r="O155" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P155" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="156" spans="11:16">
+      <c r="K156" t="s">
+        <v>68</v>
+      </c>
+      <c r="L156" s="1"/>
+      <c r="M156" t="s">
+        <v>729</v>
+      </c>
+      <c r="N156" s="1"/>
+      <c r="O156" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="157" spans="11:16">
+      <c r="K157" t="s">
+        <v>137</v>
+      </c>
+      <c r="L157" s="1"/>
+      <c r="M157" t="s">
+        <v>726</v>
+      </c>
+      <c r="N157" s="1"/>
+      <c r="O157" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P157">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="158" spans="11:16">
+      <c r="K158" t="s">
+        <v>119</v>
+      </c>
+      <c r="M158" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="159" spans="11:16">
+      <c r="K159" t="s">
+        <v>116</v>
+      </c>
+      <c r="M159" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="162" spans="11:18">
+      <c r="K162">
+        <v>100</v>
+      </c>
+      <c r="L162" t="s">
+        <v>4</v>
+      </c>
+      <c r="N162" t="s">
+        <v>4</v>
+      </c>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="163" spans="11:18">
+      <c r="K163" t="s">
+        <v>0</v>
+      </c>
+      <c r="L163" s="12">
+        <v>4</v>
+      </c>
+      <c r="M163" t="s">
+        <v>1</v>
+      </c>
+      <c r="N163" s="12">
+        <v>5</v>
+      </c>
+      <c r="O163" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P163" t="s">
+        <v>366</v>
+      </c>
+      <c r="R163" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="164" spans="11:18">
+      <c r="K164" t="s">
+        <v>66</v>
+      </c>
+      <c r="L164" s="12"/>
+      <c r="M164" t="s">
+        <v>675</v>
+      </c>
+      <c r="N164" s="12"/>
+      <c r="O164" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="165" spans="11:18">
+      <c r="K165" t="s">
+        <v>70</v>
+      </c>
+      <c r="L165" s="12"/>
+      <c r="M165" t="s">
+        <v>676</v>
+      </c>
+      <c r="N165" s="12"/>
+      <c r="O165" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="166" spans="11:18">
+      <c r="K166" t="s">
+        <v>72</v>
+      </c>
+      <c r="M166" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="167" spans="11:18">
+      <c r="K167" t="s">
+        <v>117</v>
+      </c>
+      <c r="M167" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="38">
+    <mergeCell ref="L163:L165"/>
+    <mergeCell ref="N163:N165"/>
+    <mergeCell ref="L61:L63"/>
+    <mergeCell ref="N61:N63"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="N69:N71"/>
+    <mergeCell ref="L74:L76"/>
+    <mergeCell ref="N74:N76"/>
+    <mergeCell ref="B56:B63"/>
+    <mergeCell ref="D56:D63"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="D2:D9"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="D24:D31"/>
+    <mergeCell ref="N2:N12"/>
+    <mergeCell ref="L2:L12"/>
+    <mergeCell ref="L15:L33"/>
+    <mergeCell ref="N15:N33"/>
     <mergeCell ref="B99:B106"/>
     <mergeCell ref="D99:D106"/>
     <mergeCell ref="B66:B73"/>
@@ -2438,16 +8250,1679 @@
     <mergeCell ref="D35:D42"/>
     <mergeCell ref="B45:B52"/>
     <mergeCell ref="D45:D52"/>
-    <mergeCell ref="B56:B63"/>
-    <mergeCell ref="D56:D63"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="D2:D9"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="D24:D31"/>
+    <mergeCell ref="L49:L51"/>
+    <mergeCell ref="N49:N51"/>
+    <mergeCell ref="N37:N39"/>
+    <mergeCell ref="L37:L39"/>
+    <mergeCell ref="L43:L45"/>
+    <mergeCell ref="N43:N45"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD69651D-03AF-4054-878A-EAC16440115F}">
+  <dimension ref="A1:J107"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="41.42578125" customWidth="1"/>
+    <col min="7" max="7" width="27.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>184</v>
+      </c>
+      <c r="H4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>215</v>
+      </c>
+      <c r="H8" t="s">
+        <v>215</v>
+      </c>
+      <c r="I8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>215</v>
+      </c>
+      <c r="H10" t="s">
+        <v>215</v>
+      </c>
+      <c r="I10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>215</v>
+      </c>
+      <c r="H11" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>215</v>
+      </c>
+      <c r="H12" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75">
+      <c r="A13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B13" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>227</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H13" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75">
+      <c r="A14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>230</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>230</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H15" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75">
+      <c r="A16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>224</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>230</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H16" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75">
+      <c r="A17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>223</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>230</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H17" t="s">
+        <v>233</v>
+      </c>
+      <c r="I17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>247</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>258</v>
+      </c>
+      <c r="H19" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>258</v>
+      </c>
+      <c r="H20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>249</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>258</v>
+      </c>
+      <c r="H21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>257</v>
+      </c>
+      <c r="B22" t="s">
+        <v>242</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>250</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>258</v>
+      </c>
+      <c r="H22" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>258</v>
+      </c>
+      <c r="H23" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>257</v>
+      </c>
+      <c r="B24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>252</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>258</v>
+      </c>
+      <c r="H24" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s">
+        <v>245</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>258</v>
+      </c>
+      <c r="H25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>257</v>
+      </c>
+      <c r="B26" t="s">
+        <v>246</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>258</v>
+      </c>
+      <c r="H26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>257</v>
+      </c>
+      <c r="B27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>258</v>
+      </c>
+      <c r="H27" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="E28" s="6"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>266</v>
+      </c>
+      <c r="B31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>261</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>268</v>
+      </c>
+      <c r="B32" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>265</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G32" t="s">
+        <v>274</v>
+      </c>
+      <c r="I32" s="4"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B33" t="s">
+        <v>263</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>264</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G33" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>376</v>
+      </c>
+      <c r="B37" t="s">
+        <v>372</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>368</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
+      </c>
+      <c r="F37" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>376</v>
+      </c>
+      <c r="B38" t="s">
+        <v>373</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>369</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>377</v>
+      </c>
+      <c r="B41" t="s">
+        <v>374</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>370</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
+      </c>
+      <c r="F41" t="s">
+        <v>378</v>
+      </c>
+      <c r="G41" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>379</v>
+      </c>
+      <c r="B42" t="s">
+        <v>375</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>371</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>380</v>
+      </c>
+      <c r="G42" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>383</v>
+      </c>
+      <c r="B45" t="s">
+        <v>382</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
+        <v>381</v>
+      </c>
+      <c r="E45">
+        <v>3</v>
+      </c>
+      <c r="F45" t="s">
+        <v>384</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>405</v>
+      </c>
+      <c r="B48" t="s">
+        <v>385</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>396</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48" t="s">
+        <v>406</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>405</v>
+      </c>
+      <c r="B49" t="s">
+        <v>386</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>397</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="G49" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>405</v>
+      </c>
+      <c r="B50" t="s">
+        <v>387</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50" t="s">
+        <v>398</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>405</v>
+      </c>
+      <c r="B51" t="s">
+        <v>388</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>399</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>405</v>
+      </c>
+      <c r="B52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>400</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>405</v>
+      </c>
+      <c r="B53" t="s">
+        <v>390</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>401</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>405</v>
+      </c>
+      <c r="B54" t="s">
+        <v>391</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>402</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>405</v>
+      </c>
+      <c r="B55" t="s">
+        <v>392</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>403</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>405</v>
+      </c>
+      <c r="B56" t="s">
+        <v>393</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>404</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>405</v>
+      </c>
+      <c r="B57" t="s">
+        <v>394</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>395</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>49</v>
+      </c>
+      <c r="B60" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" t="s">
+        <v>185</v>
+      </c>
+      <c r="G60" t="s">
+        <v>232</v>
+      </c>
+      <c r="H60" t="s">
+        <v>186</v>
+      </c>
+      <c r="I60" t="s">
+        <v>175</v>
+      </c>
+      <c r="J60" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>450</v>
+      </c>
+      <c r="B61" t="s">
+        <v>448</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>449</v>
+      </c>
+      <c r="E61">
+        <v>4</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="H61" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>483</v>
+      </c>
+      <c r="B63" t="s">
+        <v>475</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>479</v>
+      </c>
+      <c r="E63">
+        <v>4</v>
+      </c>
+      <c r="F63" t="s">
+        <v>483</v>
+      </c>
+      <c r="G63" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>483</v>
+      </c>
+      <c r="B64" t="s">
+        <v>476</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>480</v>
+      </c>
+      <c r="E64">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>483</v>
+      </c>
+      <c r="B65" t="s">
+        <v>477</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>481</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>483</v>
+      </c>
+      <c r="B66" t="s">
+        <v>478</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>482</v>
+      </c>
+      <c r="E66">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>535</v>
+      </c>
+      <c r="B69" t="s">
+        <v>533</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>534</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>603</v>
+      </c>
+      <c r="G69" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>568</v>
+      </c>
+      <c r="B72" t="s">
+        <v>564</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>566</v>
+      </c>
+      <c r="E72">
+        <v>4</v>
+      </c>
+      <c r="F72" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>568</v>
+      </c>
+      <c r="B73" t="s">
+        <v>565</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>567</v>
+      </c>
+      <c r="E73">
+        <v>4</v>
+      </c>
+      <c r="F73" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>607</v>
+      </c>
+      <c r="B75" t="s">
+        <v>599</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>603</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+      <c r="F75" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>607</v>
+      </c>
+      <c r="B76" t="s">
+        <v>600</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>604</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>607</v>
+      </c>
+      <c r="B77" t="s">
+        <v>601</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>605</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>607</v>
+      </c>
+      <c r="B78" t="s">
+        <v>602</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>606</v>
+      </c>
+      <c r="E78">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>405</v>
+      </c>
+      <c r="B80" t="s">
+        <v>609</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80" t="s">
+        <v>611</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80" t="s">
+        <v>406</v>
+      </c>
+      <c r="G80" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>405</v>
+      </c>
+      <c r="B81" t="s">
+        <v>610</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81" t="s">
+        <v>612</v>
+      </c>
+      <c r="E81">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>616</v>
+      </c>
+      <c r="B83" t="s">
+        <v>614</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>613</v>
+      </c>
+      <c r="E83">
+        <v>4</v>
+      </c>
+      <c r="F83" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>619</v>
+      </c>
+      <c r="B85" t="s">
+        <v>617</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85" t="s">
+        <v>618</v>
+      </c>
+      <c r="E85">
+        <v>4</v>
+      </c>
+      <c r="F85" t="s">
+        <v>620</v>
+      </c>
+      <c r="G85" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>483</v>
+      </c>
+      <c r="B88" t="s">
+        <v>653</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>657</v>
+      </c>
+      <c r="E88">
+        <v>5</v>
+      </c>
+      <c r="F88" t="s">
+        <v>483</v>
+      </c>
+      <c r="G88" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>483</v>
+      </c>
+      <c r="B89" t="s">
+        <v>654</v>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89" t="s">
+        <v>658</v>
+      </c>
+      <c r="E89">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>483</v>
+      </c>
+      <c r="B90" t="s">
+        <v>655</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90" t="s">
+        <v>659</v>
+      </c>
+      <c r="E90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>483</v>
+      </c>
+      <c r="B91" t="s">
+        <v>656</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>660</v>
+      </c>
+      <c r="E91">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>535</v>
+      </c>
+      <c r="B93" t="s">
+        <v>703</v>
+      </c>
+      <c r="C93">
+        <v>4</v>
+      </c>
+      <c r="D93" t="s">
+        <v>704</v>
+      </c>
+      <c r="E93">
+        <v>5</v>
+      </c>
+      <c r="F93">
+        <v>603</v>
+      </c>
+      <c r="G93" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>568</v>
+      </c>
+      <c r="B96" t="s">
+        <v>730</v>
+      </c>
+      <c r="C96">
+        <v>4</v>
+      </c>
+      <c r="D96" t="s">
+        <v>732</v>
+      </c>
+      <c r="E96">
+        <v>5</v>
+      </c>
+      <c r="F96" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>568</v>
+      </c>
+      <c r="B97" t="s">
+        <v>731</v>
+      </c>
+      <c r="C97">
+        <v>4</v>
+      </c>
+      <c r="D97" t="s">
+        <v>733</v>
+      </c>
+      <c r="E97">
+        <v>5</v>
+      </c>
+      <c r="F97" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>607</v>
+      </c>
+      <c r="B99" t="s">
+        <v>734</v>
+      </c>
+      <c r="C99">
+        <v>4</v>
+      </c>
+      <c r="D99" t="s">
+        <v>738</v>
+      </c>
+      <c r="E99">
+        <v>5</v>
+      </c>
+      <c r="F99" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>607</v>
+      </c>
+      <c r="B100" t="s">
+        <v>735</v>
+      </c>
+      <c r="C100">
+        <v>4</v>
+      </c>
+      <c r="D100" t="s">
+        <v>739</v>
+      </c>
+      <c r="E100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>607</v>
+      </c>
+      <c r="B101" t="s">
+        <v>736</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101" t="s">
+        <v>740</v>
+      </c>
+      <c r="E101">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>607</v>
+      </c>
+      <c r="B102" t="s">
+        <v>737</v>
+      </c>
+      <c r="C102">
+        <v>4</v>
+      </c>
+      <c r="D102" t="s">
+        <v>741</v>
+      </c>
+      <c r="E102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>616</v>
+      </c>
+      <c r="B105" t="s">
+        <v>192</v>
+      </c>
+      <c r="C105">
+        <v>3</v>
+      </c>
+      <c r="D105" t="s">
+        <v>742</v>
+      </c>
+      <c r="E105">
+        <v>4</v>
+      </c>
+      <c r="F105" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>619</v>
+      </c>
+      <c r="B107" t="s">
+        <v>744</v>
+      </c>
+      <c r="C107">
+        <v>3</v>
+      </c>
+      <c r="D107" t="s">
+        <v>743</v>
+      </c>
+      <c r="E107">
+        <v>4</v>
+      </c>
+      <c r="F107" t="s">
+        <v>620</v>
+      </c>
+      <c r="G107" t="s">
+        <v>621</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
+++ b/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projet Kicad\Barre_de_Son_Dolby_DIY\Amplificateur_Audio\Amplificateur_Audio_Custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B436A2C-1AFE-48DA-9C8E-9769B52265EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CBEB61-7393-4C3F-B46E-116E58614FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Condensateur" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2438" uniqueCount="1297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="1300">
   <si>
     <t>Ref Ti</t>
   </si>
@@ -3929,6 +3929,15 @@
   </si>
   <si>
     <t>Connector_PinHeader_2.54mm:PinHeader_2x25_P2.54mm_Vertical_SMD</t>
+  </si>
+  <si>
+    <t>EEV-FK1H102M</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:CP_Elec_16x17.5</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -4016,7 +4025,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4045,7 +4054,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6607,7 +6615,7 @@
         <v>2</v>
       </c>
       <c r="F141" t="s">
-        <v>545</v>
+        <v>1297</v>
       </c>
       <c r="N141" t="s">
         <v>0</v>
@@ -6625,7 +6633,7 @@
         <v>2</v>
       </c>
       <c r="S141" t="s">
-        <v>545</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -6641,7 +6649,7 @@
         <v>1206</v>
       </c>
       <c r="F142" t="s">
-        <v>494</v>
+        <v>1298</v>
       </c>
       <c r="N142" t="s">
         <v>702</v>
@@ -6655,7 +6663,7 @@
         <v>1206</v>
       </c>
       <c r="S142" t="s">
-        <v>494</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -8834,15 +8842,6 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="379" spans="14:19">
-      <c r="N379" s="16"/>
-    </row>
-    <row r="380" spans="14:19">
-      <c r="N380" s="16"/>
-    </row>
-    <row r="381" spans="14:19">
-      <c r="N381" s="16"/>
-    </row>
     <row r="382" spans="14:19">
       <c r="N382" t="s">
         <v>3</v>
@@ -8883,9 +8882,6 @@
         <v>511</v>
       </c>
     </row>
-    <row r="385" spans="14:19">
-      <c r="N385" s="16"/>
-    </row>
     <row r="386" spans="14:19">
       <c r="N386" t="s">
         <v>414</v>
@@ -9147,6 +9143,78 @@
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="O169:O176"/>
+    <mergeCell ref="Q169:Q176"/>
+    <mergeCell ref="O141:O142"/>
+    <mergeCell ref="Q141:Q142"/>
+    <mergeCell ref="O147:O154"/>
+    <mergeCell ref="Q147:Q154"/>
+    <mergeCell ref="O158:O165"/>
+    <mergeCell ref="Q158:Q165"/>
+    <mergeCell ref="O121:O122"/>
+    <mergeCell ref="Q121:Q122"/>
+    <mergeCell ref="O125:O126"/>
+    <mergeCell ref="Q125:Q126"/>
+    <mergeCell ref="O131:O138"/>
+    <mergeCell ref="Q131:Q138"/>
+    <mergeCell ref="O95:O102"/>
+    <mergeCell ref="Q95:Q102"/>
+    <mergeCell ref="O105:O112"/>
+    <mergeCell ref="Q105:Q112"/>
+    <mergeCell ref="O115:O116"/>
+    <mergeCell ref="Q115:Q116"/>
+    <mergeCell ref="O73:O74"/>
+    <mergeCell ref="Q73:Q74"/>
+    <mergeCell ref="O79:O80"/>
+    <mergeCell ref="Q79:Q80"/>
+    <mergeCell ref="O84:O91"/>
+    <mergeCell ref="Q84:Q91"/>
+    <mergeCell ref="O44:O51"/>
+    <mergeCell ref="Q44:Q51"/>
+    <mergeCell ref="O55:O62"/>
+    <mergeCell ref="Q55:Q62"/>
+    <mergeCell ref="O67:O69"/>
+    <mergeCell ref="Q67:Q69"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="D79:D80"/>
+    <mergeCell ref="B44:B51"/>
+    <mergeCell ref="D44:D51"/>
+    <mergeCell ref="B55:B62"/>
+    <mergeCell ref="D55:D62"/>
+    <mergeCell ref="D67:D69"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="B29:B36"/>
+    <mergeCell ref="D29:D36"/>
+    <mergeCell ref="K15:K22"/>
+    <mergeCell ref="D2:D9"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B15:B22"/>
+    <mergeCell ref="D15:D22"/>
+    <mergeCell ref="I15:I22"/>
+    <mergeCell ref="B84:B91"/>
+    <mergeCell ref="D84:D91"/>
+    <mergeCell ref="B95:B102"/>
+    <mergeCell ref="D95:D102"/>
+    <mergeCell ref="B105:B112"/>
+    <mergeCell ref="D105:D112"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="D115:D116"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="D121:D122"/>
+    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="D125:D126"/>
+    <mergeCell ref="B158:B165"/>
+    <mergeCell ref="D158:D165"/>
+    <mergeCell ref="B169:B176"/>
+    <mergeCell ref="D169:D176"/>
+    <mergeCell ref="B131:B138"/>
+    <mergeCell ref="D131:D138"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="D141:D142"/>
+    <mergeCell ref="B147:B154"/>
+    <mergeCell ref="D147:D154"/>
     <mergeCell ref="O259:O266"/>
     <mergeCell ref="Q259:Q266"/>
     <mergeCell ref="O180:O187"/>
@@ -9159,78 +9227,6 @@
     <mergeCell ref="Q231:Q238"/>
     <mergeCell ref="Q248:Q255"/>
     <mergeCell ref="O248:O255"/>
-    <mergeCell ref="B158:B165"/>
-    <mergeCell ref="D158:D165"/>
-    <mergeCell ref="B169:B176"/>
-    <mergeCell ref="D169:D176"/>
-    <mergeCell ref="B131:B138"/>
-    <mergeCell ref="D131:D138"/>
-    <mergeCell ref="B141:B142"/>
-    <mergeCell ref="D141:D142"/>
-    <mergeCell ref="B147:B154"/>
-    <mergeCell ref="D147:D154"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="D115:D116"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="B125:B126"/>
-    <mergeCell ref="D125:D126"/>
-    <mergeCell ref="B84:B91"/>
-    <mergeCell ref="D84:D91"/>
-    <mergeCell ref="B95:B102"/>
-    <mergeCell ref="D95:D102"/>
-    <mergeCell ref="B105:B112"/>
-    <mergeCell ref="D105:D112"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="D29:D36"/>
-    <mergeCell ref="K15:K22"/>
-    <mergeCell ref="D2:D9"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B15:B22"/>
-    <mergeCell ref="D15:D22"/>
-    <mergeCell ref="I15:I22"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="D79:D80"/>
-    <mergeCell ref="B44:B51"/>
-    <mergeCell ref="D44:D51"/>
-    <mergeCell ref="B55:B62"/>
-    <mergeCell ref="D55:D62"/>
-    <mergeCell ref="D67:D69"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="O44:O51"/>
-    <mergeCell ref="Q44:Q51"/>
-    <mergeCell ref="O55:O62"/>
-    <mergeCell ref="Q55:Q62"/>
-    <mergeCell ref="O67:O69"/>
-    <mergeCell ref="Q67:Q69"/>
-    <mergeCell ref="O73:O74"/>
-    <mergeCell ref="Q73:Q74"/>
-    <mergeCell ref="O79:O80"/>
-    <mergeCell ref="Q79:Q80"/>
-    <mergeCell ref="O84:O91"/>
-    <mergeCell ref="Q84:Q91"/>
-    <mergeCell ref="O95:O102"/>
-    <mergeCell ref="Q95:Q102"/>
-    <mergeCell ref="O105:O112"/>
-    <mergeCell ref="Q105:Q112"/>
-    <mergeCell ref="O115:O116"/>
-    <mergeCell ref="Q115:Q116"/>
-    <mergeCell ref="O121:O122"/>
-    <mergeCell ref="Q121:Q122"/>
-    <mergeCell ref="O125:O126"/>
-    <mergeCell ref="Q125:Q126"/>
-    <mergeCell ref="O131:O138"/>
-    <mergeCell ref="Q131:Q138"/>
-    <mergeCell ref="O169:O176"/>
-    <mergeCell ref="Q169:Q176"/>
-    <mergeCell ref="O141:O142"/>
-    <mergeCell ref="Q141:Q142"/>
-    <mergeCell ref="O147:O154"/>
-    <mergeCell ref="Q147:Q154"/>
-    <mergeCell ref="O158:O165"/>
-    <mergeCell ref="Q158:Q165"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10488,6 +10484,9 @@
       <c r="E71" s="2" t="s">
         <v>74</v>
       </c>
+      <c r="H71" t="s">
+        <v>1299</v>
+      </c>
       <c r="L71" s="15"/>
       <c r="N71" s="15"/>
       <c r="O71" s="2"/>
@@ -13325,12 +13324,26 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="L49:L51"/>
-    <mergeCell ref="N49:N51"/>
-    <mergeCell ref="N37:N39"/>
-    <mergeCell ref="L37:L39"/>
-    <mergeCell ref="L43:L45"/>
-    <mergeCell ref="N43:N45"/>
+    <mergeCell ref="L198:L200"/>
+    <mergeCell ref="N198:N200"/>
+    <mergeCell ref="L205:L207"/>
+    <mergeCell ref="N205:N207"/>
+    <mergeCell ref="L163:L165"/>
+    <mergeCell ref="N163:N165"/>
+    <mergeCell ref="L61:L63"/>
+    <mergeCell ref="N61:N63"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="N69:N71"/>
+    <mergeCell ref="L74:L76"/>
+    <mergeCell ref="N74:N76"/>
+    <mergeCell ref="B56:B63"/>
+    <mergeCell ref="D56:D63"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="D2:D9"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="D14:D21"/>
+    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="D24:D31"/>
     <mergeCell ref="N2:N12"/>
     <mergeCell ref="L2:L12"/>
     <mergeCell ref="L15:L33"/>
@@ -13347,26 +13360,12 @@
     <mergeCell ref="D35:D42"/>
     <mergeCell ref="B45:B52"/>
     <mergeCell ref="D45:D52"/>
-    <mergeCell ref="B56:B63"/>
-    <mergeCell ref="D56:D63"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="D2:D9"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="D14:D21"/>
-    <mergeCell ref="B24:B31"/>
-    <mergeCell ref="D24:D31"/>
-    <mergeCell ref="L61:L63"/>
-    <mergeCell ref="N61:N63"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="N69:N71"/>
-    <mergeCell ref="L74:L76"/>
-    <mergeCell ref="N74:N76"/>
-    <mergeCell ref="L198:L200"/>
-    <mergeCell ref="N198:N200"/>
-    <mergeCell ref="L205:L207"/>
-    <mergeCell ref="N205:N207"/>
-    <mergeCell ref="L163:L165"/>
-    <mergeCell ref="N163:N165"/>
+    <mergeCell ref="L49:L51"/>
+    <mergeCell ref="N49:N51"/>
+    <mergeCell ref="N37:N39"/>
+    <mergeCell ref="L37:L39"/>
+    <mergeCell ref="L43:L45"/>
+    <mergeCell ref="N43:N45"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
+++ b/Amplificateur_Audio/Amplificateur_Audio_Custom/Comparaison ref TI et Carte Custom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projet Kicad\Barre_de_Son_Dolby_DIY\Amplificateur_Audio\Amplificateur_Audio_Custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CBEB61-7393-4C3F-B46E-116E58614FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD18497-283C-48C9-B7EE-5F4BC143D635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
+    <workbookView xWindow="-14505" yWindow="15" windowWidth="14610" windowHeight="15240" xr2:uid="{4FF8DD7E-34FE-43DF-B954-455528221A4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Condensateur" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="1300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2439" uniqueCount="1302">
   <si>
     <t>Ref Ti</t>
   </si>
@@ -3938,6 +3938,12 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>C409</t>
+  </si>
+  <si>
+    <t>CAP_EEVFK1H102M</t>
   </si>
 </sst>
 </file>
@@ -5286,7 +5292,7 @@
       </c>
       <c r="B59" s="15"/>
       <c r="C59" t="s">
-        <v>473</v>
+        <v>1300</v>
       </c>
       <c r="D59" s="15"/>
       <c r="N59" t="s">
@@ -6649,7 +6655,7 @@
         <v>1206</v>
       </c>
       <c r="F142" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="N142" t="s">
         <v>702</v>
